--- a/Onboarding/onboarding-tracker.xlsx
+++ b/Onboarding/onboarding-tracker.xlsx
@@ -1,25 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://classerasa-my.sharepoint.com/personal/m_serag_classera_com/Documents/AY26 Classera PS Training Unit Initiatives &amp; Activities/AY26-27 eLearning Plan/Outputs/plans-site V261001.3 IntelSFI &amp; Onboarding/Onboarding/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_078885AAA5B2B04D242B14369344045063DF4AD2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE79A65B-C627-4BDC-B58C-18FA77E8EE75}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Guide" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Products" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Tracks" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Lists" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Summary" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Guide" sheetId="1" r:id="rId1"/>
+    <sheet name="Products" sheetId="2" r:id="rId2"/>
+    <sheet name="Tracks" sheetId="3" r:id="rId3"/>
+    <sheet name="Lists" sheetId="4" r:id="rId4"/>
+    <sheet name="Summary" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Products!$A$1:$K$7</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Tracks!$A$1:$Q$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Products!$A$1:$K$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Tracks!$A$1:$Q$31</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -27,13 +43,13 @@
 </workbook>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -41,11 +57,11 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Never change an existing key. Tracks are matched to products by this value.</t>
+          <t>Never change an existing key. Tracks are matched to products by this value.</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -53,7 +69,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Host only, no https:// and no trailing slash. Example: elearning.classera.com</t>
+          <t>Host only, no https:// and no trailing slash. Example: elearning.classera.com</t>
         </r>
       </text>
     </comment>
@@ -61,13 +77,13 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="O1" authorId="0">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -75,11 +91,11 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Paste the full course or learning-path URL. Leave empty and the button opens the platform sign-in with a 'coming soon' note.</t>
+          <t>Paste the full course or learning-path URL. Leave empty and the button opens the platform sign-in with a 'coming soon' note.</t>
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0">
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -87,7 +103,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Optional. The matching user-manual page. Leave empty to hide the 'Read the manual' button.</t>
+          <t>Optional. The matching user-manual page. Leave empty to hide the 'Read the manual' button.</t>
         </r>
       </text>
     </comment>
@@ -96,995 +112,1000 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="326">
-  <si>
-    <t xml:space="preserve">Classera Onboarding Hub - content control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">onboarding.classera.com  |  edit this file, the site follows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How to publish a change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.  Edit the Products or Tracks sheet below. Save.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.  On GitHub, open the site repository and click Add file &gt; Upload files.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.  Drop this file in, renamed exactly onboarding-tracker.xlsx. It replaces the old one.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.  Click Commit changes. The site refreshes within about a minute.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What each sheet controls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Products   One row per card in step 1. Order sets the position. Platform Host is where the track opens.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracks     One row per track card in step 3. The role chips in step 2 are built from this sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lists      The allowed values. Do not rename them.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary    Live counts. Read only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rules that keep it working</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Never change an existing Site Key. It is how a row stays matched to its card.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keep the column headers exactly as they are. Add rows, never columns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Key on a track row must match a Site Key on the Products sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A role appears in step 2 as soon as one track row uses its Role Key. Role Order sets the chip order.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Course Link empty: the button opens the platform sign-in and shows 'Course link will be updated soon'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manual Link empty: the 'Read the manual' button is hidden for that track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status Hidden: the row disappears from the site. Coming soon: shown, button disabled.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If this file is missing or cannot be read, the site shows its built-in content instead. Nothing breaks.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Everything in this file is public once uploaded. Keep anything confidential out of it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product (EN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product (AR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (EN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description (AR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Icon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Host</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login Path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Management System (LMS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نظام إدارة التعلم LMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digital classes, assignments, assessment and parent communication.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الفصول الرقمية، الواجبات، التقييم، والتواصل مع أولياء الأمور.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cyan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">elearning.classera.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Training Management System (TMS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نظام إدارة التدريب TMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plan training programs, registration, attendance and certificates.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تخطيط البرامج التدريبية، التسجيل، الحضور، والشهادات.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">leadxeratraining.classera.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">erp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C-SmarX ERP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نظام إدارة المؤسسة C-SmarX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admissions, finance, human resources and procurement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">القبول والتسجيل، المالية، الموارد البشرية، والمشتريات.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">csmarxtraining.classera.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C-Pay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C-Pay للمدفوعات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digital fee collection, installment plans and settlements.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تحصيل الرسوم إلكترونياً، خطط التقسيط، والتسويات.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">edumalls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edumalls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The education marketplace: content, services and school products.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المتجر التعليمي: المحتوى، الخدمات، والمنتجات المدرسية.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cinspire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C-Inspire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A gamified points system that rewards students for behavior, participation and achievement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نظام نقاط محفّز يكافئ الطلاب على السلوك والمشاركة والإنجاز.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role Key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role Order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role (EN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role (AR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Track Order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Track (EN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Track (AR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minutes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Course Link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manual Link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lms-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">teacher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teacher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">معلم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMS Essentials for Teachers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أساسيات LMS للمعلم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build your class, upload content, schedule sessions and track attendance.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إنشاء الفصل، رفع المحتوى، جدولة الحصص، ومتابعة الحضور.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Essential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://manual.classera.com/docs-category/teacher-account/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lms-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assessment and Grading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التقييم والدرجات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Question banks, online exams, auto-grading and performance reports.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بنوك الأسئلة، الاختبارات الإلكترونية، الرصد التلقائي، وتقارير الأداء.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://manual.classera.com/docs-category/grade-management-teacher/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lms-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">School Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">قائد مدرسة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leadership Dashboards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لوحات المتابعة للقيادة المدرسية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Read usage KPIs, monitor teacher activity and make data-driven decisions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">قراءة مؤشرات الاستخدام، متابعة أداء المعلمين، واتخاذ قرار مبني على البيانات.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://manual.classera.com/docs-category/manager-account/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lms-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">طالب</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Quick Start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دليل الطالب للبدء</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sign in, assignments, quizzes and reaching your teacher.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الدخول، الواجبات، الاختبارات، والتواصل مع المعلم.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://manual.classera.com/docs-category/student-account/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lms-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ولي أمر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parent Quick Start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دليل ولي الأمر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Follow attendance, grades and school communication from the app.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">متابعة الحضور والدرجات والتواصل مع المدرسة من التطبيق.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://manual.classera.com/docs-category/parent-account/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lms-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">itadmin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مسؤول النظام</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Setup and Administration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إعداد وإدارة المنصة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account structure, roles and permissions, bulk import and integrations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">هيكلة الحسابات، الأدوار والصلاحيات، الاستيراد الجماعي، والتكاملات.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://manual.classera.com/docs-category/administrator-account/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tms-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trmanager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Training Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مدير التدريب</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Building a Training Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بناء البرنامج التدريبي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Courses, paths, schedules, rooms and resources.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الدورات، المسارات، الجداول، والقاعات والموارد.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://usermanual.leadxera.com/docs-category/administrator/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tms-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Training Reports and Impact KPIs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تقارير التدريب ومؤشرات الأثر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completion rates, attendance, satisfaction and cost per training hour.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">معدلات الإتمام، الحضور، رضا المتدربين، وتكلفة الساعة التدريبية.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tms-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instructor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مدرب</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainer Guide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دليل المدرب</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run the session, mark attendance, deliver materials and assess trainees.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إدارة الجلسة، رصد الحضور، تسليم المواد، وتقييم المتدربين.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://usermanual.leadxera.com/docs-category/trainer/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tms-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trainee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">متدرب</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee Guide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دليل المتدرب</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enroll in programs, track progress and download your certificate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التسجيل في البرامج، متابعة التقدم، وتحميل الشهادة.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://usermanual.leadxera.com/docs-category/trainees/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tms-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">corporate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corporate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">جهة مؤسسية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Managing Your People</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إدارة منسوبيك</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enroll your team, follow progress and pull enrollment reports.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تسجيل فريقك، متابعة التقدم، واستخراج تقارير التسجيل.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://usermanual.leadxera.com/docs-category/corporate/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">erp-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finance Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مدير مالي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core Finance Cycle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الدورة المالية الأساسية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuition fees, invoicing, collections and financial reporting.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الرسوم الدراسية، الفوترة، التحصيل، والتقارير المالية.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">erp-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budgeting and Financial Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الموازنات والتحليل المالي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build budgets, compare plan vs actual and analyze variances.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بناء الموازنة، مقارنة المخطط بالفعلي، وتحليل الانحرافات.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">erp-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">registrar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registrar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">شؤون الطلاب</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admissions and Registration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">القبول والتسجيل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student file, enrollment, class allocation and official documents.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ملف الطالب، التسجيل، توزيع الفصول، والوثائق الرسمية.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">erp-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hrofficer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR Officer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">موظف موارد بشرية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إدارة شؤون الموظفين</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employee file, attendance and leave, and payroll.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ملف الموظف، الحضور والإجازات، والرواتب.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://usermanual.csmarx.com/docs-category/human-resources/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">erp-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">procure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المشتريات والمخازن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procurement and Inventory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المشتريات والمخزون</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purchase orders, vendors, receiving and asset inventory.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أوامر الشراء، الموردون، الاستلام، وجرد الأصول.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">erp-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Setup and Permissions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إعداد النظام والصلاحيات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Org structure, approval cycles and module-level permissions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الهيكل التنظيمي، دورات الاعتماد، والصلاحيات على مستوى الوحدة.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpay-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">finofficer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finance Officer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">موظف مالي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activating Digital Collection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تفعيل التحصيل الإلكتروني</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link fees, issue payment links and run daily follow-up.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ربط الرسوم، إصدار روابط الدفع، والمتابعة اليومية.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://manual.classera.com/docs-category/school-accountant/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpay-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reconciliation and Reporting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التسويات والتقارير</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Match payments, bank settlement and collection reports.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مطابقة المدفوعات، التسويات البنكية، وتقارير التحصيل.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpay-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cashier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cashier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أمين صندوق</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cashier Guide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دليل أمين الصندوق</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On-site payments, receipts and refunds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الدفع الحضوري، الإيصالات، والاسترجاع.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpay-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paying as a Parent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الدفع لولي الأمر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">View your invoice, pay online and use installment plans.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عرض الفاتورة، الدفع الإلكتروني، وخطط التقسيط.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://manual.classera.com/docs-category/c-pay-parent/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">edu-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">storemgr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Store Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مدير المتجر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setting Up Your Store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تجهيز المتجر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalog, pricing, offers and order management.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الكتالوج، التسعير، العروض، وإدارة الطلبات.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coming soon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">edu-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">publisher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Content Publisher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ناشر محتوى</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publishing Educational Content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نشر المحتوى التعليمي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload content, quality standards, rights and revenue share.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">رفع المحتوى، معايير الجودة، والحقوق ومشاركة الإيراد.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">edu-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تحليل المبيعات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product performance, conversion rate and pricing decisions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أداء المنتجات، معدل التحويل، وقرارات التسعير.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">edu-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">buyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buyer / Parent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مشتري / ولي أمر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buyer Guide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دليل الشراء</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search, order, pay and track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">البحث، الطلب، الدفع، والمتابعة.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cin-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activity Officer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مسؤول الأنشطة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setting Up the Points System</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إعداد نظام النقاط</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Define point categories, values, levels and the reward catalog for your school.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تحديد فئات النقاط وقيمها ومستوياتها وقائمة المكافآت الخاصة بمدرستك.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://manual.classera.com/docs-category/c-inspire-awards-activity-officer/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cin-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rewards, Badges and Leaderboards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المكافآت والشارات ولوحات الصدارة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design reward tiers, publish leaderboards and run seasonal point campaigns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تصميم مستويات المكافآت، نشر لوحات الصدارة، وإطلاق حملات نقاط موسمية.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cin-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Awarding Points in Class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">منح النقاط داخل الفصل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Give and withdraw points, use quick actions, and keep awarding fair and consistent.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">منح النقاط وسحبها، استخدام الإجراءات السريعة، والحفاظ على عدالة المنح واتساقه.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://manual.classera.com/docs-category/c-inspire/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cin-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earning and Spending Your Points</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اكسب نقاطك واستبدلها</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Track your balance, climb the leaderboard, and redeem points for rewards and badges.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تابع رصيدك، تقدّم في لوحة الصدارة، واستبدل نقاطك بالمكافآت والشارات.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://manual.classera.com/docs-category/c-inspire-awards-and-scores-student/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cin-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Following Your Child's Points</t>
-  </si>
-  <si>
-    <t xml:space="preserve">متابعة نقاط أبنائك</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See points earned, the reasons behind them, and your child's standing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اطّلع على النقاط المكتسبة وأسبابها وترتيب ابنك.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://manual.classera.com/docs-category/c-inspire-awards-parent/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hidden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coverage at a glance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Counts update automatically from the Tracks sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live tracks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Course links set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manual links set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="329">
+  <si>
+    <t>Classera Onboarding Hub - content control</t>
+  </si>
+  <si>
+    <t>onboarding.classera.com  |  edit this file, the site follows</t>
+  </si>
+  <si>
+    <t>How to publish a change</t>
+  </si>
+  <si>
+    <t>1.  Edit the Products or Tracks sheet below. Save.</t>
+  </si>
+  <si>
+    <t>2.  On GitHub, open the site repository and click Add file &gt; Upload files.</t>
+  </si>
+  <si>
+    <t>3.  Drop this file in, renamed exactly onboarding-tracker.xlsx. It replaces the old one.</t>
+  </si>
+  <si>
+    <t>4.  Click Commit changes. The site refreshes within about a minute.</t>
+  </si>
+  <si>
+    <t>What each sheet controls</t>
+  </si>
+  <si>
+    <t>Products   One row per card in step 1. Order sets the position. Platform Host is where the track opens.</t>
+  </si>
+  <si>
+    <t>Tracks     One row per track card in step 3. The role chips in step 2 are built from this sheet.</t>
+  </si>
+  <si>
+    <t>Lists      The allowed values. Do not rename them.</t>
+  </si>
+  <si>
+    <t>Summary    Live counts. Read only.</t>
+  </si>
+  <si>
+    <t>Rules that keep it working</t>
+  </si>
+  <si>
+    <t>Never change an existing Site Key. It is how a row stays matched to its card.</t>
+  </si>
+  <si>
+    <t>Keep the column headers exactly as they are. Add rows, never columns.</t>
+  </si>
+  <si>
+    <t>Product Key on a track row must match a Site Key on the Products sheet.</t>
+  </si>
+  <si>
+    <t>A role appears in step 2 as soon as one track row uses its Role Key. Role Order sets the chip order.</t>
+  </si>
+  <si>
+    <t>Course Link empty: the button opens the platform sign-in and shows 'Course link will be updated soon'.</t>
+  </si>
+  <si>
+    <t>Manual Link empty: the 'Read the manual' button is hidden for that track.</t>
+  </si>
+  <si>
+    <t>Status Hidden: the row disappears from the site. Coming soon: shown, button disabled.</t>
+  </si>
+  <si>
+    <t>If this file is missing or cannot be read, the site shows its built-in content instead. Nothing breaks.</t>
+  </si>
+  <si>
+    <t>Everything in this file is public once uploaded. Keep anything confidential out of it.</t>
+  </si>
+  <si>
+    <t>Site Key</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>Product (EN)</t>
+  </si>
+  <si>
+    <t>Product (AR)</t>
+  </si>
+  <si>
+    <t>Description (EN)</t>
+  </si>
+  <si>
+    <t>Description (AR)</t>
+  </si>
+  <si>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>Accent</t>
+  </si>
+  <si>
+    <t>Platform Host</t>
+  </si>
+  <si>
+    <t>Login Path</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>lms</t>
+  </si>
+  <si>
+    <t>Learning Management System (LMS)</t>
+  </si>
+  <si>
+    <t>نظام إدارة التعلم LMS</t>
+  </si>
+  <si>
+    <t>Digital classes, assignments, assessment and parent communication.</t>
+  </si>
+  <si>
+    <t>الفصول الرقمية، الواجبات، التقييم، والتواصل مع أولياء الأمور.</t>
+  </si>
+  <si>
+    <t>cyan</t>
+  </si>
+  <si>
+    <t>elearning.classera.com</t>
+  </si>
+  <si>
+    <t>/login</t>
+  </si>
+  <si>
+    <t>Live</t>
+  </si>
+  <si>
+    <t>tms</t>
+  </si>
+  <si>
+    <t>Training Management System (TMS)</t>
+  </si>
+  <si>
+    <t>نظام إدارة التدريب TMS</t>
+  </si>
+  <si>
+    <t>Plan training programs, registration, attendance and certificates.</t>
+  </si>
+  <si>
+    <t>تخطيط البرامج التدريبية، التسجيل، الحضور، والشهادات.</t>
+  </si>
+  <si>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>leadxeratraining.classera.com</t>
+  </si>
+  <si>
+    <t>erp</t>
+  </si>
+  <si>
+    <t>C-SmarX ERP</t>
+  </si>
+  <si>
+    <t>نظام إدارة المؤسسة C-SmarX</t>
+  </si>
+  <si>
+    <t>Admissions, finance, human resources and procurement.</t>
+  </si>
+  <si>
+    <t>القبول والتسجيل، المالية، الموارد البشرية، والمشتريات.</t>
+  </si>
+  <si>
+    <t>gold</t>
+  </si>
+  <si>
+    <t>csmarxtraining.classera.com</t>
+  </si>
+  <si>
+    <t>cpay</t>
+  </si>
+  <si>
+    <t>C-Pay</t>
+  </si>
+  <si>
+    <t>C-Pay للمدفوعات</t>
+  </si>
+  <si>
+    <t>Digital fee collection, installment plans and settlements.</t>
+  </si>
+  <si>
+    <t>تحصيل الرسوم إلكترونياً، خطط التقسيط، والتسويات.</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>green</t>
+  </si>
+  <si>
+    <t>edumalls</t>
+  </si>
+  <si>
+    <t>Edumalls</t>
+  </si>
+  <si>
+    <t>The education marketplace: content, services and school products.</t>
+  </si>
+  <si>
+    <t>المتجر التعليمي: المحتوى، الخدمات، والمنتجات المدرسية.</t>
+  </si>
+  <si>
+    <t>mall</t>
+  </si>
+  <si>
+    <t>cinspire</t>
+  </si>
+  <si>
+    <t>C-Inspire</t>
+  </si>
+  <si>
+    <t>A gamified points system that rewards students for behavior, participation and achievement.</t>
+  </si>
+  <si>
+    <t>نظام نقاط محفّز يكافئ الطلاب على السلوك والمشاركة والإنجاز.</t>
+  </si>
+  <si>
+    <t>spark</t>
+  </si>
+  <si>
+    <t>Product Key</t>
+  </si>
+  <si>
+    <t>Role Key</t>
+  </si>
+  <si>
+    <t>Role Order</t>
+  </si>
+  <si>
+    <t>Role (EN)</t>
+  </si>
+  <si>
+    <t>Role (AR)</t>
+  </si>
+  <si>
+    <t>Track Order</t>
+  </si>
+  <si>
+    <t>Track (EN)</t>
+  </si>
+  <si>
+    <t>Track (AR)</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Modules</t>
+  </si>
+  <si>
+    <t>Minutes</t>
+  </si>
+  <si>
+    <t>Course Link</t>
+  </si>
+  <si>
+    <t>Manual Link</t>
+  </si>
+  <si>
+    <t>lms-01</t>
+  </si>
+  <si>
+    <t>teacher</t>
+  </si>
+  <si>
+    <t>Teacher</t>
+  </si>
+  <si>
+    <t>معلم</t>
+  </si>
+  <si>
+    <t>LMS Essentials for Teachers</t>
+  </si>
+  <si>
+    <t>أساسيات LMS للمعلم</t>
+  </si>
+  <si>
+    <t>Build your class, upload content, schedule sessions and track attendance.</t>
+  </si>
+  <si>
+    <t>إنشاء الفصل، رفع المحتوى، جدولة الحصص، ومتابعة الحضور.</t>
+  </si>
+  <si>
+    <t>Essential</t>
+  </si>
+  <si>
+    <t>https://manual.classera.com/docs-category/teacher-account/</t>
+  </si>
+  <si>
+    <t>lms-02</t>
+  </si>
+  <si>
+    <t>Assessment and Grading</t>
+  </si>
+  <si>
+    <t>التقييم والدرجات</t>
+  </si>
+  <si>
+    <t>Question banks, online exams, auto-grading and performance reports.</t>
+  </si>
+  <si>
+    <t>بنوك الأسئلة، الاختبارات الإلكترونية، الرصد التلقائي، وتقارير الأداء.</t>
+  </si>
+  <si>
+    <t>Core</t>
+  </si>
+  <si>
+    <t>https://manual.classera.com/docs-category/grade-management-teacher/</t>
+  </si>
+  <si>
+    <t>lms-03</t>
+  </si>
+  <si>
+    <t>leader</t>
+  </si>
+  <si>
+    <t>School Leader</t>
+  </si>
+  <si>
+    <t>قائد مدرسة</t>
+  </si>
+  <si>
+    <t>Leadership Dashboards</t>
+  </si>
+  <si>
+    <t>لوحات المتابعة للقيادة المدرسية</t>
+  </si>
+  <si>
+    <t>Read usage KPIs, monitor teacher activity and make data-driven decisions.</t>
+  </si>
+  <si>
+    <t>قراءة مؤشرات الاستخدام، متابعة أداء المعلمين، واتخاذ قرار مبني على البيانات.</t>
+  </si>
+  <si>
+    <t>https://manual.classera.com/docs-category/manager-account/</t>
+  </si>
+  <si>
+    <t>lms-04</t>
+  </si>
+  <si>
+    <t>student</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>طالب</t>
+  </si>
+  <si>
+    <t>Student Quick Start</t>
+  </si>
+  <si>
+    <t>دليل الطالب للبدء</t>
+  </si>
+  <si>
+    <t>Sign in, assignments, quizzes and reaching your teacher.</t>
+  </si>
+  <si>
+    <t>الدخول، الواجبات، الاختبارات، والتواصل مع المعلم.</t>
+  </si>
+  <si>
+    <t>https://manual.classera.com/docs-category/student-account/</t>
+  </si>
+  <si>
+    <t>lms-05</t>
+  </si>
+  <si>
+    <t>parent</t>
+  </si>
+  <si>
+    <t>Parent</t>
+  </si>
+  <si>
+    <t>ولي أمر</t>
+  </si>
+  <si>
+    <t>Parent Quick Start</t>
+  </si>
+  <si>
+    <t>دليل ولي الأمر</t>
+  </si>
+  <si>
+    <t>Follow attendance, grades and school communication from the app.</t>
+  </si>
+  <si>
+    <t>متابعة الحضور والدرجات والتواصل مع المدرسة من التطبيق.</t>
+  </si>
+  <si>
+    <t>https://manual.classera.com/docs-category/parent-account/</t>
+  </si>
+  <si>
+    <t>lms-06</t>
+  </si>
+  <si>
+    <t>itadmin</t>
+  </si>
+  <si>
+    <t>System Admin</t>
+  </si>
+  <si>
+    <t>مسؤول النظام</t>
+  </si>
+  <si>
+    <t>Platform Setup and Administration</t>
+  </si>
+  <si>
+    <t>إعداد وإدارة المنصة</t>
+  </si>
+  <si>
+    <t>Account structure, roles and permissions, bulk import and integrations.</t>
+  </si>
+  <si>
+    <t>هيكلة الحسابات، الأدوار والصلاحيات، الاستيراد الجماعي، والتكاملات.</t>
+  </si>
+  <si>
+    <t>Advanced</t>
+  </si>
+  <si>
+    <t>https://manual.classera.com/docs-category/administrator-account/</t>
+  </si>
+  <si>
+    <t>tms-01</t>
+  </si>
+  <si>
+    <t>trmanager</t>
+  </si>
+  <si>
+    <t>Training Manager</t>
+  </si>
+  <si>
+    <t>مدير التدريب</t>
+  </si>
+  <si>
+    <t>Building a Training Program</t>
+  </si>
+  <si>
+    <t>بناء البرنامج التدريبي</t>
+  </si>
+  <si>
+    <t>Courses, paths, schedules, rooms and resources.</t>
+  </si>
+  <si>
+    <t>الدورات، المسارات، الجداول، والقاعات والموارد.</t>
+  </si>
+  <si>
+    <t>https://usermanual.leadxera.com/docs-category/administrator/</t>
+  </si>
+  <si>
+    <t>tms-02</t>
+  </si>
+  <si>
+    <t>Training Reports and Impact KPIs</t>
+  </si>
+  <si>
+    <t>تقارير التدريب ومؤشرات الأثر</t>
+  </si>
+  <si>
+    <t>Completion rates, attendance, satisfaction and cost per training hour.</t>
+  </si>
+  <si>
+    <t>معدلات الإتمام، الحضور، رضا المتدربين، وتكلفة الساعة التدريبية.</t>
+  </si>
+  <si>
+    <t>tms-03</t>
+  </si>
+  <si>
+    <t>instructor</t>
+  </si>
+  <si>
+    <t>Trainer</t>
+  </si>
+  <si>
+    <t>مدرب</t>
+  </si>
+  <si>
+    <t>Trainer Guide</t>
+  </si>
+  <si>
+    <t>دليل المدرب</t>
+  </si>
+  <si>
+    <t>Run the session, mark attendance, deliver materials and assess trainees.</t>
+  </si>
+  <si>
+    <t>إدارة الجلسة، رصد الحضور، تسليم المواد، وتقييم المتدربين.</t>
+  </si>
+  <si>
+    <t>https://usermanual.leadxera.com/docs-category/trainer/</t>
+  </si>
+  <si>
+    <t>tms-04</t>
+  </si>
+  <si>
+    <t>trainee</t>
+  </si>
+  <si>
+    <t>Trainee</t>
+  </si>
+  <si>
+    <t>متدرب</t>
+  </si>
+  <si>
+    <t>Trainee Guide</t>
+  </si>
+  <si>
+    <t>دليل المتدرب</t>
+  </si>
+  <si>
+    <t>Enroll in programs, track progress and download your certificate.</t>
+  </si>
+  <si>
+    <t>التسجيل في البرامج، متابعة التقدم، وتحميل الشهادة.</t>
+  </si>
+  <si>
+    <t>https://usermanual.leadxera.com/docs-category/trainees/</t>
+  </si>
+  <si>
+    <t>tms-05</t>
+  </si>
+  <si>
+    <t>corporate</t>
+  </si>
+  <si>
+    <t>Corporate</t>
+  </si>
+  <si>
+    <t>جهة مؤسسية</t>
+  </si>
+  <si>
+    <t>Managing Your People</t>
+  </si>
+  <si>
+    <t>إدارة منسوبيك</t>
+  </si>
+  <si>
+    <t>Enroll your team, follow progress and pull enrollment reports.</t>
+  </si>
+  <si>
+    <t>تسجيل فريقك، متابعة التقدم، واستخراج تقارير التسجيل.</t>
+  </si>
+  <si>
+    <t>https://usermanual.leadxera.com/docs-category/corporate/</t>
+  </si>
+  <si>
+    <t>erp-01</t>
+  </si>
+  <si>
+    <t>finance</t>
+  </si>
+  <si>
+    <t>Finance Manager</t>
+  </si>
+  <si>
+    <t>مدير مالي</t>
+  </si>
+  <si>
+    <t>Core Finance Cycle</t>
+  </si>
+  <si>
+    <t>الدورة المالية الأساسية</t>
+  </si>
+  <si>
+    <t>Tuition fees, invoicing, collections and financial reporting.</t>
+  </si>
+  <si>
+    <t>الرسوم الدراسية، الفوترة، التحصيل، والتقارير المالية.</t>
+  </si>
+  <si>
+    <t>erp-02</t>
+  </si>
+  <si>
+    <t>Budgeting and Financial Analysis</t>
+  </si>
+  <si>
+    <t>الموازنات والتحليل المالي</t>
+  </si>
+  <si>
+    <t>Build budgets, compare plan vs actual and analyze variances.</t>
+  </si>
+  <si>
+    <t>بناء الموازنة، مقارنة المخطط بالفعلي، وتحليل الانحرافات.</t>
+  </si>
+  <si>
+    <t>erp-03</t>
+  </si>
+  <si>
+    <t>registrar</t>
+  </si>
+  <si>
+    <t>Registrar</t>
+  </si>
+  <si>
+    <t>شؤون الطلاب</t>
+  </si>
+  <si>
+    <t>Admissions and Registration</t>
+  </si>
+  <si>
+    <t>القبول والتسجيل</t>
+  </si>
+  <si>
+    <t>Student file, enrollment, class allocation and official documents.</t>
+  </si>
+  <si>
+    <t>ملف الطالب، التسجيل، توزيع الفصول، والوثائق الرسمية.</t>
+  </si>
+  <si>
+    <t>erp-04</t>
+  </si>
+  <si>
+    <t>hrofficer</t>
+  </si>
+  <si>
+    <t>HR Officer</t>
+  </si>
+  <si>
+    <t>موظف موارد بشرية</t>
+  </si>
+  <si>
+    <t>HR Operations</t>
+  </si>
+  <si>
+    <t>إدارة شؤون الموظفين</t>
+  </si>
+  <si>
+    <t>Employee file, attendance and leave, and payroll.</t>
+  </si>
+  <si>
+    <t>ملف الموظف، الحضور والإجازات، والرواتب.</t>
+  </si>
+  <si>
+    <t>https://usermanual.csmarx.com/docs-category/human-resources/</t>
+  </si>
+  <si>
+    <t>erp-05</t>
+  </si>
+  <si>
+    <t>procure</t>
+  </si>
+  <si>
+    <t>Procurement</t>
+  </si>
+  <si>
+    <t>المشتريات والمخازن</t>
+  </si>
+  <si>
+    <t>Procurement and Inventory</t>
+  </si>
+  <si>
+    <t>المشتريات والمخزون</t>
+  </si>
+  <si>
+    <t>Purchase orders, vendors, receiving and asset inventory.</t>
+  </si>
+  <si>
+    <t>أوامر الشراء، الموردون، الاستلام، وجرد الأصول.</t>
+  </si>
+  <si>
+    <t>erp-06</t>
+  </si>
+  <si>
+    <t>System Setup and Permissions</t>
+  </si>
+  <si>
+    <t>إعداد النظام والصلاحيات</t>
+  </si>
+  <si>
+    <t>Org structure, approval cycles and module-level permissions.</t>
+  </si>
+  <si>
+    <t>الهيكل التنظيمي، دورات الاعتماد، والصلاحيات على مستوى الوحدة.</t>
+  </si>
+  <si>
+    <t>cpay-01</t>
+  </si>
+  <si>
+    <t>finofficer</t>
+  </si>
+  <si>
+    <t>Finance Officer</t>
+  </si>
+  <si>
+    <t>موظف مالي</t>
+  </si>
+  <si>
+    <t>Activating Digital Collection</t>
+  </si>
+  <si>
+    <t>تفعيل التحصيل الإلكتروني</t>
+  </si>
+  <si>
+    <t>Link fees, issue payment links and run daily follow-up.</t>
+  </si>
+  <si>
+    <t>ربط الرسوم، إصدار روابط الدفع، والمتابعة اليومية.</t>
+  </si>
+  <si>
+    <t>https://manual.classera.com/docs-category/school-accountant/</t>
+  </si>
+  <si>
+    <t>cpay-02</t>
+  </si>
+  <si>
+    <t>Reconciliation and Reporting</t>
+  </si>
+  <si>
+    <t>التسويات والتقارير</t>
+  </si>
+  <si>
+    <t>Match payments, bank settlement and collection reports.</t>
+  </si>
+  <si>
+    <t>مطابقة المدفوعات، التسويات البنكية، وتقارير التحصيل.</t>
+  </si>
+  <si>
+    <t>cpay-03</t>
+  </si>
+  <si>
+    <t>cashier</t>
+  </si>
+  <si>
+    <t>Cashier</t>
+  </si>
+  <si>
+    <t>أمين صندوق</t>
+  </si>
+  <si>
+    <t>Cashier Guide</t>
+  </si>
+  <si>
+    <t>دليل أمين الصندوق</t>
+  </si>
+  <si>
+    <t>On-site payments, receipts and refunds.</t>
+  </si>
+  <si>
+    <t>الدفع الحضوري، الإيصالات، والاسترجاع.</t>
+  </si>
+  <si>
+    <t>cpay-04</t>
+  </si>
+  <si>
+    <t>Paying as a Parent</t>
+  </si>
+  <si>
+    <t>الدفع لولي الأمر</t>
+  </si>
+  <si>
+    <t>View your invoice, pay online and use installment plans.</t>
+  </si>
+  <si>
+    <t>عرض الفاتورة، الدفع الإلكتروني، وخطط التقسيط.</t>
+  </si>
+  <si>
+    <t>https://manual.classera.com/docs-category/c-pay-parent/</t>
+  </si>
+  <si>
+    <t>edu-01</t>
+  </si>
+  <si>
+    <t>storemgr</t>
+  </si>
+  <si>
+    <t>Store Manager</t>
+  </si>
+  <si>
+    <t>مدير المتجر</t>
+  </si>
+  <si>
+    <t>Setting Up Your Store</t>
+  </si>
+  <si>
+    <t>تجهيز المتجر</t>
+  </si>
+  <si>
+    <t>Catalog, pricing, offers and order management.</t>
+  </si>
+  <si>
+    <t>الكتالوج، التسعير، العروض، وإدارة الطلبات.</t>
+  </si>
+  <si>
+    <t>Coming soon</t>
+  </si>
+  <si>
+    <t>edu-02</t>
+  </si>
+  <si>
+    <t>publisher</t>
+  </si>
+  <si>
+    <t>Content Publisher</t>
+  </si>
+  <si>
+    <t>ناشر محتوى</t>
+  </si>
+  <si>
+    <t>Publishing Educational Content</t>
+  </si>
+  <si>
+    <t>نشر المحتوى التعليمي</t>
+  </si>
+  <si>
+    <t>Upload content, quality standards, rights and revenue share.</t>
+  </si>
+  <si>
+    <t>رفع المحتوى، معايير الجودة، والحقوق ومشاركة الإيراد.</t>
+  </si>
+  <si>
+    <t>edu-03</t>
+  </si>
+  <si>
+    <t>Sales Analytics</t>
+  </si>
+  <si>
+    <t>تحليل المبيعات</t>
+  </si>
+  <si>
+    <t>Product performance, conversion rate and pricing decisions.</t>
+  </si>
+  <si>
+    <t>أداء المنتجات، معدل التحويل، وقرارات التسعير.</t>
+  </si>
+  <si>
+    <t>edu-04</t>
+  </si>
+  <si>
+    <t>buyer</t>
+  </si>
+  <si>
+    <t>Buyer / Parent</t>
+  </si>
+  <si>
+    <t>مشتري / ولي أمر</t>
+  </si>
+  <si>
+    <t>Buyer Guide</t>
+  </si>
+  <si>
+    <t>دليل الشراء</t>
+  </si>
+  <si>
+    <t>Search, order, pay and track.</t>
+  </si>
+  <si>
+    <t>البحث، الطلب، الدفع، والمتابعة.</t>
+  </si>
+  <si>
+    <t>cin-01</t>
+  </si>
+  <si>
+    <t>activity</t>
+  </si>
+  <si>
+    <t>Activity Officer</t>
+  </si>
+  <si>
+    <t>مسؤول الأنشطة</t>
+  </si>
+  <si>
+    <t>Setting Up the Points System</t>
+  </si>
+  <si>
+    <t>إعداد نظام النقاط</t>
+  </si>
+  <si>
+    <t>Define point categories, values, levels and the reward catalog for your school.</t>
+  </si>
+  <si>
+    <t>تحديد فئات النقاط وقيمها ومستوياتها وقائمة المكافآت الخاصة بمدرستك.</t>
+  </si>
+  <si>
+    <t>https://manual.classera.com/docs-category/c-inspire-awards-activity-officer/</t>
+  </si>
+  <si>
+    <t>cin-02</t>
+  </si>
+  <si>
+    <t>Rewards, Badges and Leaderboards</t>
+  </si>
+  <si>
+    <t>المكافآت والشارات ولوحات الصدارة</t>
+  </si>
+  <si>
+    <t>Design reward tiers, publish leaderboards and run seasonal point campaigns.</t>
+  </si>
+  <si>
+    <t>تصميم مستويات المكافآت، نشر لوحات الصدارة، وإطلاق حملات نقاط موسمية.</t>
+  </si>
+  <si>
+    <t>cin-03</t>
+  </si>
+  <si>
+    <t>Awarding Points in Class</t>
+  </si>
+  <si>
+    <t>منح النقاط داخل الفصل</t>
+  </si>
+  <si>
+    <t>Give and withdraw points, use quick actions, and keep awarding fair and consistent.</t>
+  </si>
+  <si>
+    <t>منح النقاط وسحبها، استخدام الإجراءات السريعة، والحفاظ على عدالة المنح واتساقه.</t>
+  </si>
+  <si>
+    <t>https://manual.classera.com/docs-category/c-inspire/</t>
+  </si>
+  <si>
+    <t>cin-04</t>
+  </si>
+  <si>
+    <t>Earning and Spending Your Points</t>
+  </si>
+  <si>
+    <t>اكسب نقاطك واستبدلها</t>
+  </si>
+  <si>
+    <t>Track your balance, climb the leaderboard, and redeem points for rewards and badges.</t>
+  </si>
+  <si>
+    <t>تابع رصيدك، تقدّم في لوحة الصدارة، واستبدل نقاطك بالمكافآت والشارات.</t>
+  </si>
+  <si>
+    <t>https://manual.classera.com/docs-category/c-inspire-awards-and-scores-student/</t>
+  </si>
+  <si>
+    <t>cin-05</t>
+  </si>
+  <si>
+    <t>Following Your Child's Points</t>
+  </si>
+  <si>
+    <t>متابعة نقاط أبنائك</t>
+  </si>
+  <si>
+    <t>See points earned, the reasons behind them, and your child's standing.</t>
+  </si>
+  <si>
+    <t>اطّلع على النقاط المكتسبة وأسبابها وترتيب ابنك.</t>
+  </si>
+  <si>
+    <t>https://manual.classera.com/docs-category/c-inspire-awards-parent/</t>
+  </si>
+  <si>
+    <t>Hidden</t>
+  </si>
+  <si>
+    <t>book</t>
+  </si>
+  <si>
+    <t>chart</t>
+  </si>
+  <si>
+    <t>Coverage at a glance</t>
+  </si>
+  <si>
+    <t>Counts update automatically from the Tracks sheet.</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Roles</t>
+  </si>
+  <si>
+    <t>Tracks</t>
+  </si>
+  <si>
+    <t>Live tracks</t>
+  </si>
+  <si>
+    <t>Course links set</t>
+  </si>
+  <si>
+    <t>Manual links set</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>https://elearning.classera.com/lectures-list/?course_title=Teachers%20Account%20|%20AY26&amp;course_type=2&amp;c=eyJjb3Vyc2VfaWQiOiIxMjIzNjEifQ</t>
+  </si>
+  <si>
+    <t>https://elearning.classera.com/lectures-list/?course_title=Administrator%20Account%20|%20AY26&amp;course_type=2&amp;c=eyJjb3Vyc2VfaWQiOiIxMjIzNjIifQ</t>
+  </si>
+  <si>
+    <t>https://elearning.classera.com/lectures-list/?course_title=Manager%20Account%20|%20AY26&amp;course_type=2&amp;c=eyJjb3Vyc2VfaWQiOiIxMjI0MDcifQ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-  </numFmts>
-  <fonts count="15">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1095,77 +1116,54 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="16"/>
       <color rgb="FF0E3350"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF7A8CA0"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF1E2E3A"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
       <color rgb="FF0E3350"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFD68A21"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFB4402F"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFEAF3F8"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1173,19 +1171,17 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <color rgb="FF0E3350"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1221,14 +1217,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFDCE6EE"/>
       </left>
@@ -1244,170 +1240,50 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0E3350"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE2F3F6"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEAF3F8"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F6FA"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF8E1"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{D1203BA1-0F41-4730-BDC4-19C74EFA1EEB}"/>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1466,55 +1342,67 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF1E2E3A"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1522,12 +1410,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1556,7 +1444,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1577,7 +1465,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1628,7 +1516,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1646,179 +1534,197 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="13">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{2EFE5C39-84FE-40C2-BEB7-BB969CA1AE95}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;ed0118f4-22db-4149-896a-1dd430dfaee1&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:B27"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="112"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="112" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="2:2" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="3"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="7" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="6" width="42" customWidth="1"/>
+    <col min="7" max="8" width="9" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>22</v>
       </c>
@@ -1853,11 +1759,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="9">
         <v>10</v>
       </c>
       <c r="C2" s="10" t="s">
@@ -1888,11 +1794,11 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="12">
         <v>20</v>
       </c>
       <c r="C3" s="10" t="s">
@@ -1923,11 +1829,11 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="9">
         <v>30</v>
       </c>
       <c r="C4" s="10" t="s">
@@ -1958,11 +1864,11 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="12">
         <v>40</v>
       </c>
       <c r="C5" s="10" t="s">
@@ -1993,11 +1899,11 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="9">
         <v>50</v>
       </c>
       <c r="C6" s="10" t="s">
@@ -2028,11 +1934,11 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="12">
         <v>60</v>
       </c>
       <c r="C7" s="10" t="s">
@@ -2064,59 +1970,70 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K7"/>
-  <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G7" type="list">
-      <formula1>Lists!$A$2:$A$9</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H7" type="list">
-      <formula1>Lists!$B$2:$B$5</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K7" type="list">
-      <formula1>Lists!$D$2:$D$4</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:K7" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
+          <x14:formula1>
+            <xm:f>Lists!$A$2:$A$9</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>G2:G7</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
+          <x14:formula1>
+            <xm:f>Lists!$B$2:$B$5</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>H2:H7</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000002000000}">
+          <x14:formula1>
+            <xm:f>Lists!$D$2:$D$4</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>K2:K7</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Q31"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="13"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="7" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="11" width="44" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="14" width="8" customWidth="1"/>
+    <col min="15" max="15" width="34" customWidth="1"/>
+    <col min="16" max="16" width="40" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>22</v>
       </c>
@@ -2169,7 +2086,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:17" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>86</v>
       </c>
@@ -2179,7 +2096,7 @@
       <c r="C2" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="9" t="n">
+      <c r="D2" s="9">
         <v>10</v>
       </c>
       <c r="E2" s="9" t="s">
@@ -2188,7 +2105,7 @@
       <c r="F2" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="G2" s="9" t="n">
+      <c r="G2" s="9">
         <v>10</v>
       </c>
       <c r="H2" s="10" t="s">
@@ -2206,13 +2123,15 @@
       <c r="L2" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="M2" s="9" t="n">
+      <c r="M2" s="9">
         <v>6</v>
       </c>
-      <c r="N2" s="9" t="n">
+      <c r="N2" s="9">
         <v>55</v>
       </c>
-      <c r="O2" s="10"/>
+      <c r="O2" s="10" t="s">
+        <v>326</v>
+      </c>
       <c r="P2" s="10" t="s">
         <v>95</v>
       </c>
@@ -2220,7 +2139,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>96</v>
       </c>
@@ -2230,7 +2149,7 @@
       <c r="C3" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="12" t="n">
+      <c r="D3" s="12">
         <v>10</v>
       </c>
       <c r="E3" s="12" t="s">
@@ -2239,7 +2158,7 @@
       <c r="F3" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="G3" s="12" t="n">
+      <c r="G3" s="12">
         <v>20</v>
       </c>
       <c r="H3" s="10" t="s">
@@ -2257,10 +2176,10 @@
       <c r="L3" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="M3" s="12" t="n">
+      <c r="M3" s="12">
         <v>5</v>
       </c>
-      <c r="N3" s="12" t="n">
+      <c r="N3" s="12">
         <v>45</v>
       </c>
       <c r="O3" s="10"/>
@@ -2271,7 +2190,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:17" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>103</v>
       </c>
@@ -2281,7 +2200,7 @@
       <c r="C4" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="9">
         <v>20</v>
       </c>
       <c r="E4" s="9" t="s">
@@ -2290,7 +2209,7 @@
       <c r="F4" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="9">
         <v>10</v>
       </c>
       <c r="H4" s="10" t="s">
@@ -2308,13 +2227,15 @@
       <c r="L4" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" s="9">
         <v>5</v>
       </c>
-      <c r="N4" s="9" t="n">
+      <c r="N4" s="9">
         <v>50</v>
       </c>
-      <c r="O4" s="10"/>
+      <c r="O4" s="10" t="s">
+        <v>328</v>
+      </c>
       <c r="P4" s="10" t="s">
         <v>111</v>
       </c>
@@ -2322,7 +2243,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>112</v>
       </c>
@@ -2332,7 +2253,7 @@
       <c r="C5" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="12">
         <v>30</v>
       </c>
       <c r="E5" s="12" t="s">
@@ -2341,7 +2262,7 @@
       <c r="F5" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="12">
         <v>10</v>
       </c>
       <c r="H5" s="10" t="s">
@@ -2359,10 +2280,10 @@
       <c r="L5" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="M5" s="12" t="n">
+      <c r="M5" s="12">
         <v>4</v>
       </c>
-      <c r="N5" s="12" t="n">
+      <c r="N5" s="12">
         <v>30</v>
       </c>
       <c r="O5" s="10"/>
@@ -2373,7 +2294,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>121</v>
       </c>
@@ -2383,7 +2304,7 @@
       <c r="C6" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="9">
         <v>40</v>
       </c>
       <c r="E6" s="9" t="s">
@@ -2392,7 +2313,7 @@
       <c r="F6" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="9">
         <v>10</v>
       </c>
       <c r="H6" s="10" t="s">
@@ -2410,10 +2331,10 @@
       <c r="L6" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="9">
         <v>3</v>
       </c>
-      <c r="N6" s="9" t="n">
+      <c r="N6" s="9">
         <v>25</v>
       </c>
       <c r="O6" s="10"/>
@@ -2424,7 +2345,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:17" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>130</v>
       </c>
@@ -2434,7 +2355,7 @@
       <c r="C7" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="12">
         <v>50</v>
       </c>
       <c r="E7" s="12" t="s">
@@ -2443,7 +2364,7 @@
       <c r="F7" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="12">
         <v>10</v>
       </c>
       <c r="H7" s="10" t="s">
@@ -2461,13 +2382,15 @@
       <c r="L7" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="M7" s="12" t="n">
+      <c r="M7" s="12">
         <v>7</v>
       </c>
-      <c r="N7" s="12" t="n">
+      <c r="N7" s="12">
         <v>75</v>
       </c>
-      <c r="O7" s="10"/>
+      <c r="O7" s="10" t="s">
+        <v>327</v>
+      </c>
       <c r="P7" s="10" t="s">
         <v>139</v>
       </c>
@@ -2475,7 +2398,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>140</v>
       </c>
@@ -2485,7 +2408,7 @@
       <c r="C8" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="9">
         <v>10</v>
       </c>
       <c r="E8" s="9" t="s">
@@ -2494,7 +2417,7 @@
       <c r="F8" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="9">
         <v>10</v>
       </c>
       <c r="H8" s="10" t="s">
@@ -2512,10 +2435,10 @@
       <c r="L8" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="9">
         <v>6</v>
       </c>
-      <c r="N8" s="9" t="n">
+      <c r="N8" s="9">
         <v>60</v>
       </c>
       <c r="O8" s="10"/>
@@ -2526,7 +2449,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>149</v>
       </c>
@@ -2536,7 +2459,7 @@
       <c r="C9" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="12">
         <v>10</v>
       </c>
       <c r="E9" s="12" t="s">
@@ -2545,7 +2468,7 @@
       <c r="F9" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="12">
         <v>20</v>
       </c>
       <c r="H9" s="10" t="s">
@@ -2563,10 +2486,10 @@
       <c r="L9" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="M9" s="12" t="n">
+      <c r="M9" s="12">
         <v>5</v>
       </c>
-      <c r="N9" s="12" t="n">
+      <c r="N9" s="12">
         <v>45</v>
       </c>
       <c r="O9" s="10"/>
@@ -2575,7 +2498,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>154</v>
       </c>
@@ -2585,7 +2508,7 @@
       <c r="C10" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="9">
         <v>20</v>
       </c>
       <c r="E10" s="9" t="s">
@@ -2594,7 +2517,7 @@
       <c r="F10" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="9">
         <v>10</v>
       </c>
       <c r="H10" s="10" t="s">
@@ -2612,10 +2535,10 @@
       <c r="L10" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="9">
         <v>4</v>
       </c>
-      <c r="N10" s="9" t="n">
+      <c r="N10" s="9">
         <v>35</v>
       </c>
       <c r="O10" s="10"/>
@@ -2626,7 +2549,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>163</v>
       </c>
@@ -2636,7 +2559,7 @@
       <c r="C11" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="12">
         <v>30</v>
       </c>
       <c r="E11" s="12" t="s">
@@ -2645,7 +2568,7 @@
       <c r="F11" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="12">
         <v>10</v>
       </c>
       <c r="H11" s="10" t="s">
@@ -2663,10 +2586,10 @@
       <c r="L11" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="M11" s="12">
         <v>3</v>
       </c>
-      <c r="N11" s="12" t="n">
+      <c r="N11" s="12">
         <v>20</v>
       </c>
       <c r="O11" s="10"/>
@@ -2677,7 +2600,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>172</v>
       </c>
@@ -2687,7 +2610,7 @@
       <c r="C12" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="9">
         <v>40</v>
       </c>
       <c r="E12" s="9" t="s">
@@ -2696,7 +2619,7 @@
       <c r="F12" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="9">
         <v>10</v>
       </c>
       <c r="H12" s="10" t="s">
@@ -2714,10 +2637,10 @@
       <c r="L12" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="M12" s="9" t="n">
+      <c r="M12" s="9">
         <v>3</v>
       </c>
-      <c r="N12" s="9" t="n">
+      <c r="N12" s="9">
         <v>25</v>
       </c>
       <c r="O12" s="10"/>
@@ -2728,7 +2651,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>181</v>
       </c>
@@ -2738,7 +2661,7 @@
       <c r="C13" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="12">
         <v>10</v>
       </c>
       <c r="E13" s="12" t="s">
@@ -2747,7 +2670,7 @@
       <c r="F13" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="12">
         <v>10</v>
       </c>
       <c r="H13" s="10" t="s">
@@ -2765,10 +2688,10 @@
       <c r="L13" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="M13" s="12">
         <v>6</v>
       </c>
-      <c r="N13" s="12" t="n">
+      <c r="N13" s="12">
         <v>65</v>
       </c>
       <c r="O13" s="10"/>
@@ -2777,7 +2700,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>189</v>
       </c>
@@ -2787,7 +2710,7 @@
       <c r="C14" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="9">
         <v>10</v>
       </c>
       <c r="E14" s="9" t="s">
@@ -2796,7 +2719,7 @@
       <c r="F14" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="9">
         <v>20</v>
       </c>
       <c r="H14" s="10" t="s">
@@ -2814,10 +2737,10 @@
       <c r="L14" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="M14" s="9" t="n">
+      <c r="M14" s="9">
         <v>4</v>
       </c>
-      <c r="N14" s="9" t="n">
+      <c r="N14" s="9">
         <v>45</v>
       </c>
       <c r="O14" s="10"/>
@@ -2826,7 +2749,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>194</v>
       </c>
@@ -2836,7 +2759,7 @@
       <c r="C15" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="12">
         <v>20</v>
       </c>
       <c r="E15" s="12" t="s">
@@ -2845,7 +2768,7 @@
       <c r="F15" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="12">
         <v>10</v>
       </c>
       <c r="H15" s="10" t="s">
@@ -2863,10 +2786,10 @@
       <c r="L15" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="M15" s="12">
         <v>5</v>
       </c>
-      <c r="N15" s="12" t="n">
+      <c r="N15" s="12">
         <v>50</v>
       </c>
       <c r="O15" s="10"/>
@@ -2875,7 +2798,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>202</v>
       </c>
@@ -2885,7 +2808,7 @@
       <c r="C16" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="9">
         <v>30</v>
       </c>
       <c r="E16" s="9" t="s">
@@ -2894,7 +2817,7 @@
       <c r="F16" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" s="9">
         <v>10</v>
       </c>
       <c r="H16" s="10" t="s">
@@ -2912,10 +2835,10 @@
       <c r="L16" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="M16" s="9" t="n">
+      <c r="M16" s="9">
         <v>5</v>
       </c>
-      <c r="N16" s="9" t="n">
+      <c r="N16" s="9">
         <v>50</v>
       </c>
       <c r="O16" s="10"/>
@@ -2926,7 +2849,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>211</v>
       </c>
@@ -2936,7 +2859,7 @@
       <c r="C17" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="12">
         <v>40</v>
       </c>
       <c r="E17" s="12" t="s">
@@ -2945,7 +2868,7 @@
       <c r="F17" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="G17" s="12">
         <v>10</v>
       </c>
       <c r="H17" s="10" t="s">
@@ -2963,10 +2886,10 @@
       <c r="L17" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="M17" s="12">
         <v>4</v>
       </c>
-      <c r="N17" s="12" t="n">
+      <c r="N17" s="12">
         <v>40</v>
       </c>
       <c r="O17" s="10"/>
@@ -2975,7 +2898,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>219</v>
       </c>
@@ -2985,7 +2908,7 @@
       <c r="C18" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="9">
         <v>50</v>
       </c>
       <c r="E18" s="9" t="s">
@@ -2994,7 +2917,7 @@
       <c r="F18" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="9">
         <v>10</v>
       </c>
       <c r="H18" s="10" t="s">
@@ -3012,10 +2935,10 @@
       <c r="L18" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="M18" s="9">
         <v>6</v>
       </c>
-      <c r="N18" s="9" t="n">
+      <c r="N18" s="9">
         <v>70</v>
       </c>
       <c r="O18" s="10"/>
@@ -3024,7 +2947,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>224</v>
       </c>
@@ -3034,7 +2957,7 @@
       <c r="C19" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" s="12">
         <v>10</v>
       </c>
       <c r="E19" s="12" t="s">
@@ -3043,7 +2966,7 @@
       <c r="F19" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="12">
         <v>10</v>
       </c>
       <c r="H19" s="10" t="s">
@@ -3061,10 +2984,10 @@
       <c r="L19" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="M19" s="12">
         <v>5</v>
       </c>
-      <c r="N19" s="12" t="n">
+      <c r="N19" s="12">
         <v>45</v>
       </c>
       <c r="O19" s="10"/>
@@ -3075,7 +2998,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>233</v>
       </c>
@@ -3085,7 +3008,7 @@
       <c r="C20" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="9">
         <v>10</v>
       </c>
       <c r="E20" s="9" t="s">
@@ -3094,7 +3017,7 @@
       <c r="F20" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="9">
         <v>20</v>
       </c>
       <c r="H20" s="10" t="s">
@@ -3112,10 +3035,10 @@
       <c r="L20" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="M20" s="9" t="n">
+      <c r="M20" s="9">
         <v>4</v>
       </c>
-      <c r="N20" s="9" t="n">
+      <c r="N20" s="9">
         <v>35</v>
       </c>
       <c r="O20" s="10"/>
@@ -3124,7 +3047,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>238</v>
       </c>
@@ -3134,7 +3057,7 @@
       <c r="C21" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D21" s="12">
         <v>20</v>
       </c>
       <c r="E21" s="12" t="s">
@@ -3143,7 +3066,7 @@
       <c r="F21" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="G21" s="12">
         <v>10</v>
       </c>
       <c r="H21" s="10" t="s">
@@ -3161,10 +3084,10 @@
       <c r="L21" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="M21" s="12">
         <v>3</v>
       </c>
-      <c r="N21" s="12" t="n">
+      <c r="N21" s="12">
         <v>25</v>
       </c>
       <c r="O21" s="10"/>
@@ -3173,7 +3096,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>246</v>
       </c>
@@ -3183,7 +3106,7 @@
       <c r="C22" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="9">
         <v>30</v>
       </c>
       <c r="E22" s="9" t="s">
@@ -3192,7 +3115,7 @@
       <c r="F22" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="9">
         <v>10</v>
       </c>
       <c r="H22" s="10" t="s">
@@ -3210,10 +3133,10 @@
       <c r="L22" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="M22" s="9" t="n">
+      <c r="M22" s="9">
         <v>2</v>
       </c>
-      <c r="N22" s="9" t="n">
+      <c r="N22" s="9">
         <v>15</v>
       </c>
       <c r="O22" s="10"/>
@@ -3224,7 +3147,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>252</v>
       </c>
@@ -3234,7 +3157,7 @@
       <c r="C23" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="D23" s="12">
         <v>10</v>
       </c>
       <c r="E23" s="12" t="s">
@@ -3243,7 +3166,7 @@
       <c r="F23" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="G23" s="12">
         <v>10</v>
       </c>
       <c r="H23" s="10" t="s">
@@ -3261,10 +3184,10 @@
       <c r="L23" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="M23" s="12">
         <v>5</v>
       </c>
-      <c r="N23" s="12" t="n">
+      <c r="N23" s="12">
         <v>50</v>
       </c>
       <c r="O23" s="10"/>
@@ -3273,7 +3196,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>261</v>
       </c>
@@ -3283,7 +3206,7 @@
       <c r="C24" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="9">
         <v>20</v>
       </c>
       <c r="E24" s="9" t="s">
@@ -3292,7 +3215,7 @@
       <c r="F24" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="9">
         <v>10</v>
       </c>
       <c r="H24" s="10" t="s">
@@ -3310,10 +3233,10 @@
       <c r="L24" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="M24" s="9" t="n">
+      <c r="M24" s="9">
         <v>4</v>
       </c>
-      <c r="N24" s="9" t="n">
+      <c r="N24" s="9">
         <v>40</v>
       </c>
       <c r="O24" s="10"/>
@@ -3322,7 +3245,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>269</v>
       </c>
@@ -3332,7 +3255,7 @@
       <c r="C25" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" s="12">
         <v>10</v>
       </c>
       <c r="E25" s="12" t="s">
@@ -3341,7 +3264,7 @@
       <c r="F25" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="G25" s="12">
         <v>20</v>
       </c>
       <c r="H25" s="10" t="s">
@@ -3359,10 +3282,10 @@
       <c r="L25" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="M25" s="12">
         <v>4</v>
       </c>
-      <c r="N25" s="12" t="n">
+      <c r="N25" s="12">
         <v>35</v>
       </c>
       <c r="O25" s="10"/>
@@ -3371,7 +3294,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>274</v>
       </c>
@@ -3381,7 +3304,7 @@
       <c r="C26" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="9">
         <v>30</v>
       </c>
       <c r="E26" s="9" t="s">
@@ -3390,7 +3313,7 @@
       <c r="F26" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" s="9">
         <v>10</v>
       </c>
       <c r="H26" s="10" t="s">
@@ -3408,10 +3331,10 @@
       <c r="L26" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" s="9">
         <v>2</v>
       </c>
-      <c r="N26" s="9" t="n">
+      <c r="N26" s="9">
         <v>15</v>
       </c>
       <c r="O26" s="10"/>
@@ -3420,7 +3343,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>282</v>
       </c>
@@ -3430,7 +3353,7 @@
       <c r="C27" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="D27" s="12">
         <v>10</v>
       </c>
       <c r="E27" s="12" t="s">
@@ -3439,7 +3362,7 @@
       <c r="F27" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="G27" s="12">
         <v>10</v>
       </c>
       <c r="H27" s="10" t="s">
@@ -3457,10 +3380,10 @@
       <c r="L27" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="M27" s="12">
         <v>5</v>
       </c>
-      <c r="N27" s="12" t="n">
+      <c r="N27" s="12">
         <v>45</v>
       </c>
       <c r="O27" s="10"/>
@@ -3471,7 +3394,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>291</v>
       </c>
@@ -3481,7 +3404,7 @@
       <c r="C28" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="9">
         <v>10</v>
       </c>
       <c r="E28" s="9" t="s">
@@ -3490,7 +3413,7 @@
       <c r="F28" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="9">
         <v>20</v>
       </c>
       <c r="H28" s="10" t="s">
@@ -3508,10 +3431,10 @@
       <c r="L28" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" s="9">
         <v>4</v>
       </c>
-      <c r="N28" s="9" t="n">
+      <c r="N28" s="9">
         <v>35</v>
       </c>
       <c r="O28" s="10"/>
@@ -3520,7 +3443,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>296</v>
       </c>
@@ -3530,7 +3453,7 @@
       <c r="C29" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="D29" s="12">
         <v>20</v>
       </c>
       <c r="E29" s="12" t="s">
@@ -3539,7 +3462,7 @@
       <c r="F29" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="G29" s="12">
         <v>10</v>
       </c>
       <c r="H29" s="10" t="s">
@@ -3557,10 +3480,10 @@
       <c r="L29" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="M29" s="12">
         <v>3</v>
       </c>
-      <c r="N29" s="12" t="n">
+      <c r="N29" s="12">
         <v>25</v>
       </c>
       <c r="O29" s="10"/>
@@ -3571,7 +3494,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>302</v>
       </c>
@@ -3581,7 +3504,7 @@
       <c r="C30" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="D30" s="9" t="n">
+      <c r="D30" s="9">
         <v>30</v>
       </c>
       <c r="E30" s="9" t="s">
@@ -3590,7 +3513,7 @@
       <c r="F30" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="G30" s="9" t="n">
+      <c r="G30" s="9">
         <v>10</v>
       </c>
       <c r="H30" s="10" t="s">
@@ -3608,10 +3531,10 @@
       <c r="L30" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="9">
         <v>3</v>
       </c>
-      <c r="N30" s="9" t="n">
+      <c r="N30" s="9">
         <v>20</v>
       </c>
       <c r="O30" s="10"/>
@@ -3622,7 +3545,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>308</v>
       </c>
@@ -3632,7 +3555,7 @@
       <c r="C31" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D31" s="12" t="n">
+      <c r="D31" s="12">
         <v>40</v>
       </c>
       <c r="E31" s="12" t="s">
@@ -3641,7 +3564,7 @@
       <c r="F31" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="G31" s="12">
         <v>10</v>
       </c>
       <c r="H31" s="10" t="s">
@@ -3659,10 +3582,10 @@
       <c r="L31" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="M31" s="12">
         <v>2</v>
       </c>
-      <c r="N31" s="12" t="n">
+      <c r="N31" s="12">
         <v>15</v>
       </c>
       <c r="O31" s="10"/>
@@ -3674,41 +3597,52 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q31"/>
-  <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L2:L31" type="list">
-      <formula1>Lists!$C$2:$C$4</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="Q2:Q31" type="list">
-      <formula1>Lists!$D$2:$D$4</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:Q31" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="lms"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0200-000000000000}">
+          <x14:formula1>
+            <xm:f>Lists!$C$2:$C$4</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>L2:L31</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0200-000001000000}">
+          <x14:formula1>
+            <xm:f>Lists!$D$2:$D$4</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>Q2:Q31</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="15"/>
+    <col min="1" max="4" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>28</v>
       </c>
@@ -3722,7 +3656,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>33</v>
       </c>
@@ -3736,7 +3670,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>42</v>
       </c>
@@ -3750,7 +3684,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -3764,7 +3698,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>61</v>
       </c>
@@ -3772,63 +3706,55 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>316</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:H12"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="17"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="8" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="2:8" ht="18" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="13" t="s">
         <v>319</v>
       </c>
@@ -3851,213 +3777,214 @@
         <v>324</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="16" t="s">
         <v>34</v>
       </c>
       <c r="C6" s="16" t="str">
-        <f aca="false">INDEX(Products!$K$2:$K$7,MATCH("lms",Products!$A$2:$A$7,0))</f>
+        <f>INDEX(Products!$K$2:$K$7,MATCH("lms",Products!$A$2:$A$7,0))</f>
         <v>Live</v>
       </c>
-      <c r="D6" s="16" t="n">
-        <f aca="false">SUMPRODUCT((Tracks!$B$2:$B$31="lms")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
+      <c r="D6" s="16">
+        <f>SUMPRODUCT((Tracks!$B$2:$B$31="lms")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
         <v>5</v>
       </c>
-      <c r="E6" s="16" t="n">
-        <f aca="false">COUNTIF(Tracks!$B$2:$B$31,"lms")</f>
+      <c r="E6" s="16">
+        <f>COUNTIF(Tracks!$B$2:$B$31,"lms")</f>
         <v>6</v>
       </c>
-      <c r="F6" s="16" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"lms",Tracks!$Q$2:$Q$31,"Live")</f>
+      <c r="F6" s="16">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"lms",Tracks!$Q$2:$Q$31,"Live")</f>
         <v>6</v>
       </c>
-      <c r="G6" s="16" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"lms",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="16" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"lms",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
+      <c r="G6" s="16">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"lms",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="H6" s="16">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"lms",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="14" t="str">
-        <f aca="false">INDEX(Products!$K$2:$K$7,MATCH("tms",Products!$A$2:$A$7,0))</f>
+        <f>INDEX(Products!$K$2:$K$7,MATCH("tms",Products!$A$2:$A$7,0))</f>
         <v>Live</v>
       </c>
-      <c r="D7" s="14" t="n">
-        <f aca="false">SUMPRODUCT((Tracks!$B$2:$B$31="tms")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
+      <c r="D7" s="14">
+        <f>SUMPRODUCT((Tracks!$B$2:$B$31="tms")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
         <v>4</v>
       </c>
-      <c r="E7" s="14" t="n">
-        <f aca="false">COUNTIF(Tracks!$B$2:$B$31,"tms")</f>
+      <c r="E7" s="14">
+        <f>COUNTIF(Tracks!$B$2:$B$31,"tms")</f>
         <v>5</v>
       </c>
-      <c r="F7" s="14" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"tms",Tracks!$Q$2:$Q$31,"Live")</f>
+      <c r="F7" s="14">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"tms",Tracks!$Q$2:$Q$31,"Live")</f>
         <v>5</v>
       </c>
-      <c r="G7" s="14" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"tms",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
+      <c r="G7" s="14">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"tms",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="H7" s="14" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"tms",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
+      <c r="H7" s="14">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"tms",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="16" t="s">
         <v>50</v>
       </c>
       <c r="C8" s="16" t="str">
-        <f aca="false">INDEX(Products!$K$2:$K$7,MATCH("erp",Products!$A$2:$A$7,0))</f>
+        <f>INDEX(Products!$K$2:$K$7,MATCH("erp",Products!$A$2:$A$7,0))</f>
         <v>Live</v>
       </c>
-      <c r="D8" s="16" t="n">
-        <f aca="false">SUMPRODUCT((Tracks!$B$2:$B$31="erp")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
+      <c r="D8" s="16">
+        <f>SUMPRODUCT((Tracks!$B$2:$B$31="erp")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
         <v>5</v>
       </c>
-      <c r="E8" s="16" t="n">
-        <f aca="false">COUNTIF(Tracks!$B$2:$B$31,"erp")</f>
+      <c r="E8" s="16">
+        <f>COUNTIF(Tracks!$B$2:$B$31,"erp")</f>
         <v>6</v>
       </c>
-      <c r="F8" s="16" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"erp",Tracks!$Q$2:$Q$31,"Live")</f>
+      <c r="F8" s="16">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"erp",Tracks!$Q$2:$Q$31,"Live")</f>
         <v>6</v>
       </c>
-      <c r="G8" s="16" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"erp",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
+      <c r="G8" s="16">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"erp",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="H8" s="16" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"erp",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
+      <c r="H8" s="16">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"erp",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
         <v>57</v>
       </c>
       <c r="C9" s="14" t="str">
-        <f aca="false">INDEX(Products!$K$2:$K$7,MATCH("cpay",Products!$A$2:$A$7,0))</f>
+        <f>INDEX(Products!$K$2:$K$7,MATCH("cpay",Products!$A$2:$A$7,0))</f>
         <v>Live</v>
       </c>
-      <c r="D9" s="14" t="n">
-        <f aca="false">SUMPRODUCT((Tracks!$B$2:$B$31="cpay")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
+      <c r="D9" s="14">
+        <f>SUMPRODUCT((Tracks!$B$2:$B$31="cpay")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
         <v>3</v>
       </c>
-      <c r="E9" s="14" t="n">
-        <f aca="false">COUNTIF(Tracks!$B$2:$B$31,"cpay")</f>
+      <c r="E9" s="14">
+        <f>COUNTIF(Tracks!$B$2:$B$31,"cpay")</f>
         <v>4</v>
       </c>
-      <c r="F9" s="14" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"cpay",Tracks!$Q$2:$Q$31,"Live")</f>
+      <c r="F9" s="14">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"cpay",Tracks!$Q$2:$Q$31,"Live")</f>
         <v>4</v>
       </c>
-      <c r="G9" s="14" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"cpay",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
+      <c r="G9" s="14">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"cpay",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="H9" s="14" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"cpay",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
+      <c r="H9" s="14">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"cpay",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="16" t="s">
         <v>64</v>
       </c>
       <c r="C10" s="16" t="str">
-        <f aca="false">INDEX(Products!$K$2:$K$7,MATCH("edumalls",Products!$A$2:$A$7,0))</f>
+        <f>INDEX(Products!$K$2:$K$7,MATCH("edumalls",Products!$A$2:$A$7,0))</f>
         <v>Live</v>
       </c>
-      <c r="D10" s="16" t="n">
-        <f aca="false">SUMPRODUCT((Tracks!$B$2:$B$31="edumalls")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
+      <c r="D10" s="16">
+        <f>SUMPRODUCT((Tracks!$B$2:$B$31="edumalls")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
         <v>3</v>
       </c>
-      <c r="E10" s="16" t="n">
-        <f aca="false">COUNTIF(Tracks!$B$2:$B$31,"edumalls")</f>
+      <c r="E10" s="16">
+        <f>COUNTIF(Tracks!$B$2:$B$31,"edumalls")</f>
         <v>4</v>
       </c>
-      <c r="F10" s="16" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"edumalls",Tracks!$Q$2:$Q$31,"Live")</f>
+      <c r="F10" s="16">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"edumalls",Tracks!$Q$2:$Q$31,"Live")</f>
         <v>0</v>
       </c>
-      <c r="G10" s="16" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"edumalls",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
+      <c r="G10" s="16">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"edumalls",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="H10" s="16" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"edumalls",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
+      <c r="H10" s="16">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"edumalls",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="14" t="str">
-        <f aca="false">INDEX(Products!$K$2:$K$7,MATCH("cinspire",Products!$A$2:$A$7,0))</f>
+        <f>INDEX(Products!$K$2:$K$7,MATCH("cinspire",Products!$A$2:$A$7,0))</f>
         <v>Live</v>
       </c>
-      <c r="D11" s="14" t="n">
-        <f aca="false">SUMPRODUCT((Tracks!$B$2:$B$31="cinspire")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
+      <c r="D11" s="14">
+        <f>SUMPRODUCT((Tracks!$B$2:$B$31="cinspire")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
         <v>4</v>
       </c>
-      <c r="E11" s="14" t="n">
-        <f aca="false">COUNTIF(Tracks!$B$2:$B$31,"cinspire")</f>
+      <c r="E11" s="14">
+        <f>COUNTIF(Tracks!$B$2:$B$31,"cinspire")</f>
         <v>5</v>
       </c>
-      <c r="F11" s="14" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"cinspire",Tracks!$Q$2:$Q$31,"Live")</f>
+      <c r="F11" s="14">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"cinspire",Tracks!$Q$2:$Q$31,"Live")</f>
         <v>5</v>
       </c>
-      <c r="G11" s="14" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"cinspire",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
+      <c r="G11" s="14">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"cinspire",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="H11" s="14" t="n">
-        <f aca="false">COUNTIFS(Tracks!$B$2:$B$31,"cinspire",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
+      <c r="H11" s="14">
+        <f>COUNTIFS(Tracks!$B$2:$B$31,"cinspire",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
         <v>4</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="17" t="s">
         <v>325</v>
       </c>
       <c r="C12" s="18"/>
-      <c r="D12" s="19" t="n">
-        <f aca="false">SUM(D6:D11)</f>
+      <c r="D12" s="19">
+        <f>SUM(D6:D11)</f>
         <v>24</v>
       </c>
-      <c r="E12" s="19" t="n">
-        <f aca="false">SUM(E6:E11)</f>
+      <c r="E12" s="19">
+        <f>SUM(E6:E11)</f>
         <v>30</v>
       </c>
-      <c r="F12" s="19" t="n">
-        <f aca="false">SUM(F6:F11)</f>
+      <c r="F12" s="19">
+        <f>SUM(F6:F11)</f>
         <v>26</v>
       </c>
-      <c r="G12" s="19" t="n">
-        <f aca="false">SUM(G6:G11)</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <f aca="false">SUM(H6:H11)</f>
+      <c r="G12" s="19">
+        <f>SUM(G6:G11)</f>
+        <v>3</v>
+      </c>
+      <c r="H12" s="19">
+        <f>SUM(H6:H11)</f>
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{41b2ac2a-ff0b-436b-9840-060514e3e322}" enabled="1" method="Standard" siteId="{617ac672-c8b6-4cd8-a860-5effd359ac35}" removed="0"/>
+</clbl:labelList>
 </file>
--- a/Onboarding/onboarding-tracker.xlsx
+++ b/Onboarding/onboarding-tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://classerasa-my.sharepoint.com/personal/m_serag_classera_com/Documents/AY26 Classera PS Training Unit Initiatives &amp; Activities/AY26-27 eLearning Plan/Outputs/plans-site V261001.3 IntelSFI &amp; Onboarding/Onboarding/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_078885AAA5B2B04D242B14369344045063DF4AD2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE79A65B-C627-4BDC-B58C-18FA77E8EE75}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_078885AAA5B2B04D242B14369344045063DF4AD2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D8BE396-6C59-4D4D-8A69-419D76B409EF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1095,17 +1095,17 @@
     <t>https://elearning.classera.com/lectures-list/?course_title=Teachers%20Account%20|%20AY26&amp;course_type=2&amp;c=eyJjb3Vyc2VfaWQiOiIxMjIzNjEifQ</t>
   </si>
   <si>
-    <t>https://elearning.classera.com/lectures-list/?course_title=Administrator%20Account%20|%20AY26&amp;course_type=2&amp;c=eyJjb3Vyc2VfaWQiOiIxMjIzNjIifQ</t>
-  </si>
-  <si>
     <t>https://elearning.classera.com/lectures-list/?course_title=Manager%20Account%20|%20AY26&amp;course_type=2&amp;c=eyJjb3Vyc2VfaWQiOiIxMjI0MDcifQ</t>
+  </si>
+  <si>
+    <t>https://elearning.classera.com/lectures-list/?course_title=Administrator%20Account%20|%20AY26&amp;course_type=2&amp;c=eyJjb3Vyc2VfaWQiOiIxMjIzNjIifQ/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1183,6 +1183,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1240,10 +1248,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1276,8 +1285,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1361,10 +1374,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2086,7 +2095,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="63.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>86</v>
       </c>
@@ -2139,7 +2148,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>96</v>
       </c>
@@ -2190,7 +2199,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="63.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>103</v>
       </c>
@@ -2234,7 +2243,7 @@
         <v>50</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P4" s="10" t="s">
         <v>111</v>
@@ -2243,7 +2252,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>112</v>
       </c>
@@ -2294,7 +2303,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>121</v>
       </c>
@@ -2345,7 +2354,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>130</v>
       </c>
@@ -2388,8 +2397,8 @@
       <c r="N7" s="12">
         <v>75</v>
       </c>
-      <c r="O7" s="10" t="s">
-        <v>327</v>
+      <c r="O7" s="20" t="s">
+        <v>328</v>
       </c>
       <c r="P7" s="10" t="s">
         <v>139</v>
@@ -2898,7 +2907,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>219</v>
       </c>
@@ -3597,16 +3606,19 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q31" xr:uid="{00000000-0009-0000-0000-000002000000}">
-    <filterColumn colId="1">
+  <autoFilter ref="A1:Q31" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="4">
       <filters>
-        <filter val="lms"/>
+        <filter val="System Admin"/>
       </filters>
     </filterColumn>
   </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="O7" r:id="rId1" xr:uid="{6AD4B01B-7E55-4159-923E-883E1E7D5158}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">

--- a/Onboarding/onboarding-tracker.xlsx
+++ b/Onboarding/onboarding-tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://classerasa-my.sharepoint.com/personal/m_serag_classera_com/Documents/AY26 Classera PS Training Unit Initiatives &amp; Activities/AY26-27 eLearning Plan/Outputs/plans-site V261001.3 IntelSFI &amp; Onboarding/Onboarding/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_078885AAA5B2B04D242B14369344045063DF4AD2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D8BE396-6C59-4D4D-8A69-419D76B409EF}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_078885AAA5B2B04D242B14369344045063DF4AD2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3047571-A745-4360-AEE5-345F6326837D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2021,7 +2021,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Q31"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2095,7 +2094,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="63.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>86</v>
       </c>
@@ -2133,7 +2132,7 @@
         <v>94</v>
       </c>
       <c r="M2" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N2" s="9">
         <v>55</v>
@@ -2148,7 +2147,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>96</v>
       </c>
@@ -2186,10 +2185,10 @@
         <v>101</v>
       </c>
       <c r="M3" s="12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N3" s="12">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="O3" s="10"/>
       <c r="P3" s="10" t="s">
@@ -2199,7 +2198,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="63.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>103</v>
       </c>
@@ -2237,10 +2236,10 @@
         <v>101</v>
       </c>
       <c r="M4" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N4" s="9">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="O4" s="10" t="s">
         <v>327</v>
@@ -2252,7 +2251,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>112</v>
       </c>
@@ -2289,21 +2288,17 @@
       <c r="L5" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="M5" s="12">
-        <v>4</v>
-      </c>
-      <c r="N5" s="12">
-        <v>30</v>
-      </c>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
       <c r="O5" s="10"/>
       <c r="P5" s="10" t="s">
         <v>120</v>
       </c>
       <c r="Q5" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>121</v>
       </c>
@@ -2340,18 +2335,14 @@
       <c r="L6" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="M6" s="9">
-        <v>3</v>
-      </c>
-      <c r="N6" s="9">
-        <v>25</v>
-      </c>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
       <c r="O6" s="10"/>
       <c r="P6" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="Q6" s="9" t="s">
-        <v>41</v>
+      <c r="Q6" s="12" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -2395,7 +2386,7 @@
         <v>7</v>
       </c>
       <c r="N7" s="12">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="O7" s="20" t="s">
         <v>328</v>
@@ -2407,7 +2398,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>140</v>
       </c>
@@ -2454,11 +2445,11 @@
       <c r="P8" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="Q8" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Q8" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>149</v>
       </c>
@@ -2504,10 +2495,10 @@
       <c r="O9" s="10"/>
       <c r="P9" s="10"/>
       <c r="Q9" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>154</v>
       </c>
@@ -2554,11 +2545,11 @@
       <c r="P10" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="Q10" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Q10" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>163</v>
       </c>
@@ -2606,10 +2597,10 @@
         <v>171</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>172</v>
       </c>
@@ -2656,11 +2647,11 @@
       <c r="P12" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="Q12" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Q12" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>181</v>
       </c>
@@ -2706,10 +2697,10 @@
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
       <c r="Q13" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>189</v>
       </c>
@@ -2754,11 +2745,11 @@
       </c>
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
-      <c r="Q14" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Q14" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>194</v>
       </c>
@@ -2804,10 +2795,10 @@
       <c r="O15" s="10"/>
       <c r="P15" s="10"/>
       <c r="Q15" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>202</v>
       </c>
@@ -2854,11 +2845,11 @@
       <c r="P16" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="Q16" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Q16" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>211</v>
       </c>
@@ -2904,7 +2895,7 @@
       <c r="O17" s="10"/>
       <c r="P17" s="10"/>
       <c r="Q17" s="12" t="s">
-        <v>41</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
@@ -2952,11 +2943,11 @@
       </c>
       <c r="O18" s="10"/>
       <c r="P18" s="10"/>
-      <c r="Q18" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Q18" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>224</v>
       </c>
@@ -3004,10 +2995,10 @@
         <v>232</v>
       </c>
       <c r="Q19" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>233</v>
       </c>
@@ -3052,11 +3043,11 @@
       </c>
       <c r="O20" s="10"/>
       <c r="P20" s="10"/>
-      <c r="Q20" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Q20" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>238</v>
       </c>
@@ -3102,10 +3093,10 @@
       <c r="O21" s="10"/>
       <c r="P21" s="10"/>
       <c r="Q21" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>246</v>
       </c>
@@ -3152,11 +3143,11 @@
       <c r="P22" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="Q22" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Q22" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>252</v>
       </c>
@@ -3205,7 +3196,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>261</v>
       </c>
@@ -3250,11 +3241,11 @@
       </c>
       <c r="O24" s="10"/>
       <c r="P24" s="10"/>
-      <c r="Q24" s="9" t="s">
+      <c r="Q24" s="12" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>269</v>
       </c>
@@ -3303,7 +3294,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>274</v>
       </c>
@@ -3348,11 +3339,11 @@
       </c>
       <c r="O26" s="10"/>
       <c r="P26" s="10"/>
-      <c r="Q26" s="9" t="s">
+      <c r="Q26" s="12" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>282</v>
       </c>
@@ -3400,10 +3391,10 @@
         <v>290</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>291</v>
       </c>
@@ -3448,11 +3439,11 @@
       </c>
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
-      <c r="Q28" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Q28" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>296</v>
       </c>
@@ -3500,10 +3491,10 @@
         <v>301</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>302</v>
       </c>
@@ -3550,11 +3541,11 @@
       <c r="P30" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="Q30" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Q30" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>308</v>
       </c>
@@ -3602,17 +3593,10 @@
         <v>313</v>
       </c>
       <c r="Q31" s="12" t="s">
-        <v>41</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q31" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="System Admin"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <hyperlinks>
     <hyperlink ref="O7" r:id="rId1" xr:uid="{6AD4B01B-7E55-4159-923E-883E1E7D5158}"/>
   </hyperlinks>
@@ -3807,7 +3791,7 @@
       </c>
       <c r="F6" s="16">
         <f>COUNTIFS(Tracks!$B$2:$B$31,"lms",Tracks!$Q$2:$Q$31,"Live")</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G6" s="16">
         <f>COUNTIFS(Tracks!$B$2:$B$31,"lms",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
@@ -3836,7 +3820,7 @@
       </c>
       <c r="F7" s="14">
         <f>COUNTIFS(Tracks!$B$2:$B$31,"tms",Tracks!$Q$2:$Q$31,"Live")</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G7" s="14">
         <f>COUNTIFS(Tracks!$B$2:$B$31,"tms",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
@@ -3865,7 +3849,7 @@
       </c>
       <c r="F8" s="16">
         <f>COUNTIFS(Tracks!$B$2:$B$31,"erp",Tracks!$Q$2:$Q$31,"Live")</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G8" s="16">
         <f>COUNTIFS(Tracks!$B$2:$B$31,"erp",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
@@ -3894,7 +3878,7 @@
       </c>
       <c r="F9" s="14">
         <f>COUNTIFS(Tracks!$B$2:$B$31,"cpay",Tracks!$Q$2:$Q$31,"Live")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G9" s="14">
         <f>COUNTIFS(Tracks!$B$2:$B$31,"cpay",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
@@ -3952,7 +3936,7 @@
       </c>
       <c r="F11" s="14">
         <f>COUNTIFS(Tracks!$B$2:$B$31,"cinspire",Tracks!$Q$2:$Q$31,"Live")</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G11" s="14">
         <f>COUNTIFS(Tracks!$B$2:$B$31,"cinspire",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
@@ -3978,7 +3962,7 @@
       </c>
       <c r="F12" s="19">
         <f>SUM(F6:F11)</f>
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G12" s="19">
         <f>SUM(G6:G11)</f>

--- a/Onboarding/onboarding-tracker.xlsx
+++ b/Onboarding/onboarding-tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://classerasa-my.sharepoint.com/personal/m_serag_classera_com/Documents/AY26 Classera PS Training Unit Initiatives &amp; Activities/AY26-27 eLearning Plan/Outputs/plans-site V261001.3 IntelSFI &amp; Onboarding/Onboarding/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_078885AAA5B2B04D242B14369344045063DF4AD2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3047571-A745-4360-AEE5-345F6326837D}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="11_078885AAA5B2B04D242B14369344045063DF4AD2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B099C6C-49D6-4EDC-ACD9-2704A45D54F6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Products!$A$1:$K$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Tracks!$A$1:$Q$31</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1098,14 +1098,14 @@
     <t>https://elearning.classera.com/lectures-list/?course_title=Manager%20Account%20|%20AY26&amp;course_type=2&amp;c=eyJjb3Vyc2VfaWQiOiIxMjI0MDcifQ</t>
   </si>
   <si>
-    <t>https://elearning.classera.com/lectures-list/?course_title=Administrator%20Account%20|%20AY26&amp;course_type=2&amp;c=eyJjb3Vyc2VfaWQiOiIxMjIzNjIifQ/</t>
+    <t>https://elearning.classera.com/lectures-list/?course_title=Administrator%20Account%20|%20AY26&amp;course_type=2&amp;c=eyJjb3Vyc2VfaWQiOiIxMjIzNjIifQ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1187,6 +1187,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -2021,7 +2027,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2383,7 +2389,7 @@
         <v>138</v>
       </c>
       <c r="M7" s="12">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N7" s="12">
         <v>90</v>
@@ -2398,152 +2404,186 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="D8" s="9">
+    <row r="8" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>lms-07</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>lms</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>tsupervisor</t>
+        </is>
+      </c>
+      <c r="D8" s="12">
+        <v>22</v>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Teacher Supervisor</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>مشرف تربوي</t>
+        </is>
+      </c>
+      <c r="G8" s="12">
         <v>10</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="G8" s="9">
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Supervising Teaching Quality</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>متابعة جودة التدريس</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Follow teacher activity, review lessons and assessments, and give data-based feedback.</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>متابعة نشاط المعلمين، مراجعة الدروس والتقييمات، وتقديم تغذية راجعة مبنية على البيانات.</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="12" t="inlineStr">
+        <is>
+          <t>Coming soon</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>lms-08</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>lms</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>floorsup</t>
+        </is>
+      </c>
+      <c r="D9" s="12">
+        <v>24</v>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Floor Supervisor &amp; Advisor</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>مشرف الدور والمرشد الطلابي</t>
+        </is>
+      </c>
+      <c r="G9" s="12">
         <v>10</v>
       </c>
-      <c r="H8" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="M8" s="9">
-        <v>6</v>
-      </c>
-      <c r="N8" s="9">
-        <v>60</v>
-      </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q8" s="12" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="D9" s="12">
-        <v>10</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="G9" s="12">
-        <v>20</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="L9" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="M9" s="12">
-        <v>5</v>
-      </c>
-      <c r="N9" s="12">
-        <v>45</v>
-      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Student Follow-up and Guidance</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>متابعة الطلاب والإرشاد</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>Track attendance and behavior, record student notes and communicate with parents.</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>متابعة الحضور والسلوك، تسجيل ملاحظات الطلاب، والتواصل مع أولياء الأمور.</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>Essential</t>
+        </is>
+      </c>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
       <c r="O9" s="10"/>
       <c r="P9" s="10"/>
-      <c r="Q9" s="12" t="s">
-        <v>260</v>
+      <c r="Q9" s="12" t="inlineStr">
+        <is>
+          <t>Coming soon</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="D10" s="9">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="G10" s="9">
         <v>10</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>94</v>
       </c>
       <c r="M10" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N10" s="9">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="O10" s="10"/>
       <c r="P10" s="10" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="Q10" s="12" t="s">
         <v>260</v>
@@ -2551,101 +2591,99 @@
     </row>
     <row r="11" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="D11" s="12">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="G11" s="12">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="M11" s="12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N11" s="12">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="O11" s="10"/>
-      <c r="P11" s="10" t="s">
-        <v>171</v>
-      </c>
+      <c r="P11" s="10"/>
       <c r="Q11" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="D12" s="9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="G12" s="9">
         <v>10</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="M12" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N12" s="9">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="O12" s="10"/>
       <c r="P12" s="10" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="Q12" s="12" t="s">
         <v>260</v>
@@ -2653,144 +2691,148 @@
     </row>
     <row r="13" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="D13" s="12">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="G13" s="12">
         <v>10</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="L13" s="12" t="s">
         <v>94</v>
       </c>
       <c r="M13" s="12">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N13" s="12">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
+      <c r="P13" s="10" t="s">
+        <v>171</v>
+      </c>
       <c r="Q13" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D14" s="9">
+        <v>40</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="G14" s="9">
         <v>10</v>
       </c>
-      <c r="E14" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="G14" s="9">
-        <v>20</v>
-      </c>
       <c r="H14" s="10" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="M14" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N14" s="9">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
+      <c r="P14" s="10" t="s">
+        <v>180</v>
+      </c>
       <c r="Q14" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>49</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="D15" s="12">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="G15" s="12">
         <v>10</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="L15" s="12" t="s">
         <v>94</v>
       </c>
       <c r="M15" s="12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N15" s="12">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O15" s="10"/>
       <c r="P15" s="10"/>
@@ -2800,97 +2842,95 @@
     </row>
     <row r="16" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>49</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="D16" s="9">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="G16" s="9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="M16" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N16" s="9">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O16" s="10"/>
-      <c r="P16" s="10" t="s">
-        <v>210</v>
-      </c>
+      <c r="P16" s="10"/>
       <c r="Q16" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>49</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="D17" s="12">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="G17" s="12">
         <v>10</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="M17" s="12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N17" s="12">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O17" s="10"/>
       <c r="P17" s="10"/>
@@ -2900,146 +2940,146 @@
     </row>
     <row r="18" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>49</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="D18" s="9">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="G18" s="9">
         <v>10</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="M18" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N18" s="9">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
+      <c r="P18" s="10" t="s">
+        <v>210</v>
+      </c>
       <c r="Q18" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="D19" s="12">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="G19" s="12">
         <v>10</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="M19" s="12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N19" s="12">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="O19" s="10"/>
-      <c r="P19" s="10" t="s">
-        <v>232</v>
-      </c>
+      <c r="P19" s="10"/>
       <c r="Q19" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>225</v>
+        <v>131</v>
       </c>
       <c r="D20" s="9">
+        <v>50</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G20" s="9">
         <v>10</v>
       </c>
-      <c r="E20" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="G20" s="9">
-        <v>20</v>
-      </c>
       <c r="H20" s="10" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="M20" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N20" s="9">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="O20" s="10"/>
       <c r="P20" s="10"/>
@@ -3047,148 +3087,148 @@
         <v>260</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>56</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="D21" s="12">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="G21" s="12">
         <v>10</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="L21" s="12" t="s">
         <v>94</v>
       </c>
       <c r="M21" s="12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N21" s="12">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
+      <c r="P21" s="10" t="s">
+        <v>232</v>
+      </c>
       <c r="Q21" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>122</v>
+        <v>225</v>
       </c>
       <c r="D22" s="9">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>123</v>
+        <v>226</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>124</v>
+        <v>227</v>
       </c>
       <c r="G22" s="9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="M22" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N22" s="9">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="O22" s="10"/>
-      <c r="P22" s="10" t="s">
-        <v>251</v>
-      </c>
+      <c r="P22" s="10"/>
       <c r="Q22" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D23" s="12">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="G23" s="12">
         <v>10</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="L23" s="12" t="s">
         <v>94</v>
       </c>
       <c r="M23" s="12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N23" s="12">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O23" s="10"/>
       <c r="P23" s="10"/>
@@ -3198,56 +3238,58 @@
     </row>
     <row r="24" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>262</v>
+        <v>122</v>
       </c>
       <c r="D24" s="9">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>263</v>
+        <v>123</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>264</v>
+        <v>124</v>
       </c>
       <c r="G24" s="9">
         <v>10</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="M24" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N24" s="9">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
+      <c r="P24" s="10" t="s">
+        <v>251</v>
+      </c>
       <c r="Q24" s="12" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>63</v>
@@ -3265,28 +3307,28 @@
         <v>255</v>
       </c>
       <c r="G25" s="12">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="M25" s="12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N25" s="12">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="O25" s="10"/>
       <c r="P25" s="10"/>
@@ -3294,48 +3336,48 @@
         <v>260</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>63</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="D26" s="9">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="G26" s="9">
         <v>10</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="M26" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N26" s="9">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="O26" s="10"/>
       <c r="P26" s="10"/>
@@ -3345,97 +3387,95 @@
     </row>
     <row r="27" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="D27" s="12">
         <v>10</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="G27" s="12">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="M27" s="12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N27" s="12">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="O27" s="10"/>
-      <c r="P27" s="10" t="s">
-        <v>290</v>
-      </c>
+      <c r="P27" s="10"/>
       <c r="Q27" s="12" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="D28" s="9">
+        <v>30</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G28" s="9">
         <v>10</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="G28" s="9">
-        <v>20</v>
-      </c>
       <c r="H28" s="10" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="M28" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N28" s="9">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
@@ -3445,50 +3485,50 @@
     </row>
     <row r="29" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>68</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>87</v>
+        <v>283</v>
       </c>
       <c r="D29" s="12">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>88</v>
+        <v>284</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>89</v>
+        <v>285</v>
       </c>
       <c r="G29" s="12">
         <v>10</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="M29" s="12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N29" s="12">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="O29" s="10"/>
       <c r="P29" s="10" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="Q29" s="12" t="s">
         <v>260</v>
@@ -3496,107 +3536,208 @@
     </row>
     <row r="30" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>68</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>113</v>
+        <v>283</v>
       </c>
       <c r="D30" s="9">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>114</v>
+        <v>284</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>115</v>
+        <v>285</v>
       </c>
       <c r="G30" s="9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="M30" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N30" s="9">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="O30" s="10"/>
-      <c r="P30" s="10" t="s">
-        <v>307</v>
-      </c>
+      <c r="P30" s="10"/>
       <c r="Q30" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>68</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="D31" s="12">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="G31" s="12">
         <v>10</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="L31" s="12" t="s">
         <v>94</v>
       </c>
       <c r="M31" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N31" s="12">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="O31" s="10"/>
       <c r="P31" s="10" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="Q31" s="12" t="s">
         <v>260</v>
       </c>
     </row>
+    <row r="32" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D32" s="9">
+        <v>30</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G32" s="9">
+        <v>10</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="M32" s="9">
+        <v>1</v>
+      </c>
+      <c r="N32" s="9">
+        <v>60</v>
+      </c>
+      <c r="O32" s="10"/>
+      <c r="P32" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q32" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D33" s="12">
+        <v>40</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="G33" s="12">
+        <v>10</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="L33" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="M33" s="12">
+        <v>1</v>
+      </c>
+      <c r="N33" s="12">
+        <v>60</v>
+      </c>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q33" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="O7" r:id="rId1" xr:uid="{6AD4B01B-7E55-4159-923E-883E1E7D5158}"/>
   </hyperlinks>
@@ -3613,7 +3754,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>L2:L31</xm:sqref>
+          <xm:sqref>L2:L200</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0200-000001000000}">
           <x14:formula1>
@@ -3622,7 +3763,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>Q2:Q31</xm:sqref>
+          <xm:sqref>Q2:Q200</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3782,23 +3923,23 @@
         <v>Live</v>
       </c>
       <c r="D6" s="16">
-        <f>SUMPRODUCT((Tracks!$B$2:$B$31="lms")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
+        <f>SUMPRODUCT((Tracks!$B$2:$B$200="lms")/COUNTIFS(Tracks!$B$2:$B$200,Tracks!$B$2:$B$200&amp;"",Tracks!$C$2:$C$200,Tracks!$C$2:$C$200&amp;""))</f>
         <v>5</v>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIF(Tracks!$B$2:$B$31,"lms")</f>
+        <f>COUNTIF(Tracks!$B$2:$B$200,"lms")</f>
         <v>6</v>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"lms",Tracks!$Q$2:$Q$31,"Live")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"lms",Tracks!$Q$2:$Q$200,"Live")</f>
         <v>4</v>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"lms",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"lms",Tracks!$O$2:$O$200,"&lt;&gt;")</f>
         <v>3</v>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"lms",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"lms",Tracks!$P$2:$P$200,"&lt;&gt;")</f>
         <v>6</v>
       </c>
     </row>
@@ -3811,23 +3952,23 @@
         <v>Live</v>
       </c>
       <c r="D7" s="14">
-        <f>SUMPRODUCT((Tracks!$B$2:$B$31="tms")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
+        <f>SUMPRODUCT((Tracks!$B$2:$B$200="tms")/COUNTIFS(Tracks!$B$2:$B$200,Tracks!$B$2:$B$200&amp;"",Tracks!$C$2:$C$200,Tracks!$C$2:$C$200&amp;""))</f>
         <v>4</v>
       </c>
       <c r="E7" s="14">
-        <f>COUNTIF(Tracks!$B$2:$B$31,"tms")</f>
+        <f>COUNTIF(Tracks!$B$2:$B$200,"tms")</f>
         <v>5</v>
       </c>
       <c r="F7" s="14">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"tms",Tracks!$Q$2:$Q$31,"Live")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"tms",Tracks!$Q$2:$Q$200,"Live")</f>
         <v>0</v>
       </c>
       <c r="G7" s="14">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"tms",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"tms",Tracks!$O$2:$O$200,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="H7" s="14">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"tms",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"tms",Tracks!$P$2:$P$200,"&lt;&gt;")</f>
         <v>4</v>
       </c>
     </row>
@@ -3840,23 +3981,23 @@
         <v>Live</v>
       </c>
       <c r="D8" s="16">
-        <f>SUMPRODUCT((Tracks!$B$2:$B$31="erp")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
+        <f>SUMPRODUCT((Tracks!$B$2:$B$200="erp")/COUNTIFS(Tracks!$B$2:$B$200,Tracks!$B$2:$B$200&amp;"",Tracks!$C$2:$C$200,Tracks!$C$2:$C$200&amp;""))</f>
         <v>5</v>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIF(Tracks!$B$2:$B$31,"erp")</f>
+        <f>COUNTIF(Tracks!$B$2:$B$200,"erp")</f>
         <v>6</v>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"erp",Tracks!$Q$2:$Q$31,"Live")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"erp",Tracks!$Q$2:$Q$200,"Live")</f>
         <v>0</v>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"erp",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"erp",Tracks!$O$2:$O$200,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"erp",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"erp",Tracks!$P$2:$P$200,"&lt;&gt;")</f>
         <v>1</v>
       </c>
     </row>
@@ -3869,23 +4010,23 @@
         <v>Live</v>
       </c>
       <c r="D9" s="14">
-        <f>SUMPRODUCT((Tracks!$B$2:$B$31="cpay")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
+        <f>SUMPRODUCT((Tracks!$B$2:$B$200="cpay")/COUNTIFS(Tracks!$B$2:$B$200,Tracks!$B$2:$B$200&amp;"",Tracks!$C$2:$C$200,Tracks!$C$2:$C$200&amp;""))</f>
         <v>3</v>
       </c>
       <c r="E9" s="14">
-        <f>COUNTIF(Tracks!$B$2:$B$31,"cpay")</f>
+        <f>COUNTIF(Tracks!$B$2:$B$200,"cpay")</f>
         <v>4</v>
       </c>
       <c r="F9" s="14">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"cpay",Tracks!$Q$2:$Q$31,"Live")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"cpay",Tracks!$Q$2:$Q$200,"Live")</f>
         <v>0</v>
       </c>
       <c r="G9" s="14">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"cpay",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"cpay",Tracks!$O$2:$O$200,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="H9" s="14">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"cpay",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"cpay",Tracks!$P$2:$P$200,"&lt;&gt;")</f>
         <v>2</v>
       </c>
     </row>
@@ -3898,23 +4039,23 @@
         <v>Live</v>
       </c>
       <c r="D10" s="16">
-        <f>SUMPRODUCT((Tracks!$B$2:$B$31="edumalls")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
+        <f>SUMPRODUCT((Tracks!$B$2:$B$200="edumalls")/COUNTIFS(Tracks!$B$2:$B$200,Tracks!$B$2:$B$200&amp;"",Tracks!$C$2:$C$200,Tracks!$C$2:$C$200&amp;""))</f>
         <v>3</v>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIF(Tracks!$B$2:$B$31,"edumalls")</f>
+        <f>COUNTIF(Tracks!$B$2:$B$200,"edumalls")</f>
         <v>4</v>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"edumalls",Tracks!$Q$2:$Q$31,"Live")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"edumalls",Tracks!$Q$2:$Q$200,"Live")</f>
         <v>0</v>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"edumalls",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"edumalls",Tracks!$O$2:$O$200,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"edumalls",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"edumalls",Tracks!$P$2:$P$200,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
@@ -3927,23 +4068,23 @@
         <v>Live</v>
       </c>
       <c r="D11" s="14">
-        <f>SUMPRODUCT((Tracks!$B$2:$B$31="cinspire")/COUNTIFS(Tracks!$B$2:$B$31,Tracks!$B$2:$B$31&amp;"",Tracks!$C$2:$C$31,Tracks!$C$2:$C$31&amp;""))</f>
+        <f>SUMPRODUCT((Tracks!$B$2:$B$200="cinspire")/COUNTIFS(Tracks!$B$2:$B$200,Tracks!$B$2:$B$200&amp;"",Tracks!$C$2:$C$200,Tracks!$C$2:$C$200&amp;""))</f>
         <v>4</v>
       </c>
       <c r="E11" s="14">
-        <f>COUNTIF(Tracks!$B$2:$B$31,"cinspire")</f>
+        <f>COUNTIF(Tracks!$B$2:$B$200,"cinspire")</f>
         <v>5</v>
       </c>
       <c r="F11" s="14">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"cinspire",Tracks!$Q$2:$Q$31,"Live")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"cinspire",Tracks!$Q$2:$Q$200,"Live")</f>
         <v>0</v>
       </c>
       <c r="G11" s="14">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"cinspire",Tracks!$O$2:$O$31,"&lt;&gt;")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"cinspire",Tracks!$O$2:$O$200,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="H11" s="14">
-        <f>COUNTIFS(Tracks!$B$2:$B$31,"cinspire",Tracks!$P$2:$P$31,"&lt;&gt;")</f>
+        <f>COUNTIFS(Tracks!$B$2:$B$200,"cinspire",Tracks!$P$2:$P$200,"&lt;&gt;")</f>
         <v>4</v>
       </c>
     </row>

--- a/Onboarding/onboarding-tracker.xlsx
+++ b/Onboarding/onboarding-tracker.xlsx
@@ -2027,7 +2027,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2538,139 +2538,181 @@
         </is>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="D10" s="9">
+    <row r="10" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>lms-09</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>lms</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+      <c r="D10" s="12">
         <v>10</v>
       </c>
-      <c r="E10" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="G10" s="9">
-        <v>10</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="M10" s="9">
-        <v>1</v>
-      </c>
-      <c r="N10" s="9">
-        <v>60</v>
-      </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q10" s="12" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>141</v>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Teacher</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>معلم</t>
+        </is>
+      </c>
+      <c r="G10" s="12">
+        <v>30</v>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Classera Teacher Accreditation</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>اعتماد المعلم من كلاسيرا</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Get accredited from User to Expert level: review the criteria, apply, sit the exam and earn a 3-year certificate.</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>احصل على اعتمادك من مستوى مستخدم إلى خبير: راجع المعايير، قدّم طلبك، اجتز الاختبار، واحصل على شهادة صالحة لثلاث سنوات.</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>Advanced</t>
+        </is>
+      </c>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="20" t="inlineStr">
+        <is>
+          <t>https://accreditation.classera.com/</t>
+        </is>
+      </c>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="12" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>lms-10</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>lms</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>itadmin</t>
+        </is>
       </c>
       <c r="D11" s="12">
-        <v>10</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>143</v>
+        <v>50</v>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>System Admin</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>مسؤول النظام</t>
+        </is>
       </c>
       <c r="G11" s="12">
         <v>20</v>
       </c>
-      <c r="H11" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="M11" s="12">
-        <v>1</v>
-      </c>
-      <c r="N11" s="12">
-        <v>60</v>
-      </c>
-      <c r="O11" s="10"/>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>System Manager Accreditation</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>اعتماد مدير النظام</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Get accredited as a System Manager, from Practitioner to Professional level, through criteria review, application and exam.</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>احصل على اعتماد مدير النظام من مستوى ممارس إلى محترف عبر مراجعة المعايير، تقديم الطلب، واجتياز الاختبار.</t>
+        </is>
+      </c>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>Advanced</t>
+        </is>
+      </c>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="20" t="inlineStr">
+        <is>
+          <t>https://accreditation.classera.com/</t>
+        </is>
+      </c>
       <c r="P11" s="10"/>
-      <c r="Q11" s="12" t="s">
-        <v>260</v>
+      <c r="Q11" s="12" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
       </c>
     </row>
     <row r="12" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="D12" s="9">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="G12" s="9">
         <v>10</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="L12" s="9" t="s">
         <v>94</v>
@@ -2683,7 +2725,7 @@
       </c>
       <c r="O12" s="10"/>
       <c r="P12" s="10" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="Q12" s="12" t="s">
         <v>260</v>
@@ -2691,40 +2733,40 @@
     </row>
     <row r="13" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="D13" s="12">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="G13" s="12">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="M13" s="12">
         <v>1</v>
@@ -2733,49 +2775,47 @@
         <v>60</v>
       </c>
       <c r="O13" s="10"/>
-      <c r="P13" s="10" t="s">
-        <v>171</v>
-      </c>
+      <c r="P13" s="10"/>
       <c r="Q13" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="D14" s="9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="G14" s="9">
         <v>10</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="M14" s="9">
         <v>1</v>
@@ -2785,7 +2825,7 @@
       </c>
       <c r="O14" s="10"/>
       <c r="P14" s="10" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="Q14" s="12" t="s">
         <v>260</v>
@@ -2793,37 +2833,37 @@
     </row>
     <row r="15" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="D15" s="12">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="G15" s="12">
         <v>10</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="L15" s="12" t="s">
         <v>94</v>
@@ -2835,47 +2875,49 @@
         <v>60</v>
       </c>
       <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
+      <c r="P15" s="10" t="s">
+        <v>171</v>
+      </c>
       <c r="Q15" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D16" s="9">
+        <v>40</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="G16" s="9">
         <v>10</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="G16" s="9">
-        <v>20</v>
-      </c>
       <c r="H16" s="10" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="M16" s="9">
         <v>1</v>
@@ -2884,44 +2926,46 @@
         <v>60</v>
       </c>
       <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
+      <c r="P16" s="10" t="s">
+        <v>180</v>
+      </c>
       <c r="Q16" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>49</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="D17" s="12">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="G17" s="12">
         <v>10</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="L17" s="12" t="s">
         <v>94</v>
@@ -2940,40 +2984,40 @@
     </row>
     <row r="18" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>49</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="D18" s="9">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="G18" s="9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="M18" s="9">
         <v>1</v>
@@ -2982,49 +3026,47 @@
         <v>60</v>
       </c>
       <c r="O18" s="10"/>
-      <c r="P18" s="10" t="s">
-        <v>210</v>
-      </c>
+      <c r="P18" s="10"/>
       <c r="Q18" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="D19" s="12">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="G19" s="12">
         <v>10</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="M19" s="12">
         <v>1</v>
@@ -3040,40 +3082,40 @@
     </row>
     <row r="20" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>49</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="D20" s="9">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="G20" s="9">
         <v>10</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="M20" s="9">
         <v>1</v>
@@ -3082,47 +3124,49 @@
         <v>60</v>
       </c>
       <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
+      <c r="P20" s="10" t="s">
+        <v>210</v>
+      </c>
       <c r="Q20" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="D21" s="12">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="G21" s="12">
         <v>10</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="M21" s="12">
         <v>1</v>
@@ -3131,49 +3175,47 @@
         <v>60</v>
       </c>
       <c r="O21" s="10"/>
-      <c r="P21" s="10" t="s">
-        <v>232</v>
-      </c>
+      <c r="P21" s="10"/>
       <c r="Q21" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>225</v>
+        <v>131</v>
       </c>
       <c r="D22" s="9">
+        <v>50</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G22" s="9">
         <v>10</v>
       </c>
-      <c r="E22" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="G22" s="9">
-        <v>20</v>
-      </c>
       <c r="H22" s="10" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="M22" s="9">
         <v>1</v>
@@ -3187,39 +3229,39 @@
         <v>260</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>56</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="D23" s="12">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="G23" s="12">
         <v>10</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="L23" s="12" t="s">
         <v>94</v>
@@ -3231,47 +3273,49 @@
         <v>60</v>
       </c>
       <c r="O23" s="10"/>
-      <c r="P23" s="10"/>
+      <c r="P23" s="10" t="s">
+        <v>232</v>
+      </c>
       <c r="Q23" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>56</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>122</v>
+        <v>225</v>
       </c>
       <c r="D24" s="9">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>123</v>
+        <v>226</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>124</v>
+        <v>227</v>
       </c>
       <c r="G24" s="9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="M24" s="9">
         <v>1</v>
@@ -3280,46 +3324,44 @@
         <v>60</v>
       </c>
       <c r="O24" s="10"/>
-      <c r="P24" s="10" t="s">
-        <v>251</v>
-      </c>
+      <c r="P24" s="10"/>
       <c r="Q24" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D25" s="12">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="G25" s="12">
         <v>10</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="L25" s="12" t="s">
         <v>94</v>
@@ -3338,40 +3380,40 @@
     </row>
     <row r="26" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>262</v>
+        <v>122</v>
       </c>
       <c r="D26" s="9">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>263</v>
+        <v>123</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>264</v>
+        <v>124</v>
       </c>
       <c r="G26" s="9">
         <v>10</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="M26" s="9">
         <v>1</v>
@@ -3380,14 +3422,16 @@
         <v>60</v>
       </c>
       <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
+      <c r="P26" s="10" t="s">
+        <v>251</v>
+      </c>
       <c r="Q26" s="12" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>63</v>
@@ -3405,22 +3449,22 @@
         <v>255</v>
       </c>
       <c r="G27" s="12">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="M27" s="12">
         <v>1</v>
@@ -3434,42 +3478,42 @@
         <v>260</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>63</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="D28" s="9">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="G28" s="9">
         <v>10</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="M28" s="9">
         <v>1</v>
@@ -3485,40 +3529,40 @@
     </row>
     <row r="29" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="D29" s="12">
         <v>10</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="G29" s="12">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="M29" s="12">
         <v>1</v>
@@ -3527,49 +3571,47 @@
         <v>60</v>
       </c>
       <c r="O29" s="10"/>
-      <c r="P29" s="10" t="s">
-        <v>290</v>
-      </c>
+      <c r="P29" s="10"/>
       <c r="Q29" s="12" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="D30" s="9">
+        <v>30</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G30" s="9">
         <v>10</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="G30" s="9">
-        <v>20</v>
-      </c>
       <c r="H30" s="10" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="M30" s="9">
         <v>1</v>
@@ -3585,40 +3627,40 @@
     </row>
     <row r="31" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>68</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>87</v>
+        <v>283</v>
       </c>
       <c r="D31" s="12">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>88</v>
+        <v>284</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>89</v>
+        <v>285</v>
       </c>
       <c r="G31" s="12">
         <v>10</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="M31" s="12">
         <v>1</v>
@@ -3628,7 +3670,7 @@
       </c>
       <c r="O31" s="10"/>
       <c r="P31" s="10" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="Q31" s="12" t="s">
         <v>260</v>
@@ -3636,40 +3678,40 @@
     </row>
     <row r="32" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>68</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>113</v>
+        <v>283</v>
       </c>
       <c r="D32" s="9">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>114</v>
+        <v>284</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>115</v>
+        <v>285</v>
       </c>
       <c r="G32" s="9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="M32" s="9">
         <v>1</v>
@@ -3678,46 +3720,44 @@
         <v>60</v>
       </c>
       <c r="O32" s="10"/>
-      <c r="P32" s="10" t="s">
-        <v>307</v>
-      </c>
+      <c r="P32" s="10"/>
       <c r="Q32" s="12" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>68</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="D33" s="12">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="G33" s="12">
         <v>10</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="L33" s="12" t="s">
         <v>94</v>
@@ -3730,9 +3770,111 @@
       </c>
       <c r="O33" s="10"/>
       <c r="P33" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q33" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D34" s="9">
+        <v>30</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G34" s="9">
+        <v>10</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="M34" s="9">
+        <v>1</v>
+      </c>
+      <c r="N34" s="9">
+        <v>60</v>
+      </c>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q34" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="12">
+        <v>40</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="G35" s="12">
+        <v>10</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="L35" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="M35" s="12">
+        <v>1</v>
+      </c>
+      <c r="N35" s="12">
+        <v>60</v>
+      </c>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="Q33" s="12" t="s">
+      <c r="Q35" s="12" t="s">
         <v>260</v>
       </c>
     </row>
@@ -4118,10 +4260,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{41b2ac2a-ff0b-436b-9840-060514e3e322}" enabled="1" method="Standard" siteId="{617ac672-c8b6-4cd8-a860-5effd359ac35}" removed="0"/>
-</clbl:labelList>
 </file>
--- a/Onboarding/onboarding-tracker.xlsx
+++ b/Onboarding/onboarding-tracker.xlsx
@@ -2027,7 +2027,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2045,9 +2045,10 @@
     <col min="15" max="15" width="34" customWidth="1"/>
     <col min="16" max="16" width="40" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>22</v>
       </c>
@@ -2099,8 +2100,13 @@
       <c r="Q1" s="7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>Plan Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>86</v>
       </c>
@@ -2153,7 +2159,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>96</v>
       </c>
@@ -2204,7 +2210,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>103</v>
       </c>
@@ -2257,7 +2263,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>112</v>
       </c>
@@ -2304,7 +2310,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>121</v>
       </c>
@@ -2351,7 +2357,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>130</v>
       </c>
@@ -2404,7 +2410,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>lms-07</t>
@@ -2471,7 +2477,7 @@
         </is>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>lms-08</t>
@@ -2538,7 +2544,7 @@
         </is>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>lms-09</t>
@@ -2608,8 +2614,13 @@
           <t>Live</t>
         </is>
       </c>
-    </row>
-    <row r="11" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>https://plans.classera.com/#acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>lms-10</t>
@@ -2679,8 +2690,13 @@
           <t>Live</t>
         </is>
       </c>
-    </row>
-    <row r="12" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>https://plans.classera.com/#acc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>140</v>
       </c>
@@ -2731,7 +2747,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>149</v>
       </c>
@@ -2780,7 +2796,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>154</v>
       </c>
@@ -2831,7 +2847,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>163</v>
       </c>
@@ -2882,7 +2898,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>172</v>
       </c>
@@ -2933,7 +2949,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>181</v>
       </c>
@@ -2982,7 +2998,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>189</v>
       </c>
@@ -3031,7 +3047,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>194</v>
       </c>
@@ -3080,7 +3096,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>202</v>
       </c>
@@ -3131,7 +3147,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>211</v>
       </c>
@@ -3180,7 +3196,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>219</v>
       </c>
@@ -3229,7 +3245,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>224</v>
       </c>
@@ -3280,7 +3296,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>233</v>
       </c>
@@ -3329,7 +3345,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>238</v>
       </c>
@@ -3378,7 +3394,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>246</v>
       </c>
@@ -3429,7 +3445,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>252</v>
       </c>
@@ -3478,7 +3494,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>261</v>
       </c>
@@ -3527,7 +3543,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>269</v>
       </c>
@@ -3576,7 +3592,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>274</v>
       </c>
@@ -3625,7 +3641,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>282</v>
       </c>
@@ -3676,7 +3692,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>291</v>
       </c>
@@ -3725,7 +3741,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>296</v>
       </c>
@@ -3776,7 +3792,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>302</v>
       </c>
@@ -3827,7 +3843,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>308</v>
       </c>

--- a/Onboarding/onboarding-tracker.xlsx
+++ b/Onboarding/onboarding-tracker.xlsx
@@ -1904,12 +1904,8 @@
       <c r="H5" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>40</v>
-      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
       <c r="K5" s="12" t="s">
         <v>41</v>
       </c>
@@ -1939,12 +1935,8 @@
       <c r="H6" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I6" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>40</v>
-      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
       <c r="K6" s="9" t="s">
         <v>41</v>
       </c>
@@ -1974,12 +1966,8 @@
       <c r="H7" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>40</v>
-      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
       <c r="K7" s="12" t="s">
         <v>41</v>
       </c>
